--- a/data/file/tabel_mortalita_dinamis.xlsx
+++ b/data/file/tabel_mortalita_dinamis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Kerjaan Arya\KKA VAB\Aplikasi\imbalan-pasca-kerja-app\data\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{77AB7B4A-FAF9-4E33-AAB9-8C6B9349832B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{054D1AC1-1AEF-42CE-93B3-E7BDC003A058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2C21EB3D-DA47-424B-AC62-B057914736D2}"/>
   </bookViews>
@@ -338,10 +338,10 @@
     <numFmt numFmtId="169" formatCode="0.00000"/>
     <numFmt numFmtId="170" formatCode="_(* #,##0.0000000_);_(* \(#,##0.0000000\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="171" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="173" formatCode="_(* #,##0.00000_);_(* \(#,##0.00000\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="174" formatCode="0.000%"/>
-    <numFmt numFmtId="175" formatCode="_(* #,##0.000000_);_(* \(#,##0.000000\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="_(* #,##0.000_);_(* \(#,##0.000\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="172" formatCode="_(* #,##0.00000_);_(* \(#,##0.00000\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="173" formatCode="0.000%"/>
+    <numFmt numFmtId="174" formatCode="_(* #,##0.000000_);_(* \(#,##0.000000\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="175" formatCode="_(* #,##0.000_);_(* \(#,##0.000\);_(* &quot;-&quot;_);_(@_)"/>
   </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
     <font>
@@ -450,7 +450,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -486,16 +486,16 @@
     <xf numFmtId="170" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="171" fontId="1" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="173" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="172" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="175" fontId="1" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="43" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="175" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>1</v>
@@ -3004,31 +3004,31 @@
       </c>
       <c r="P8" s="22">
         <f>+SUM(M8:$M$60)</f>
-        <v>465344.81742319983</v>
+        <v>184382.54116824438</v>
       </c>
       <c r="Q8" s="22">
         <f>+SUM(N8:$N$60)</f>
-        <v>23212.119656511517</v>
+        <v>9206.3040341638334</v>
       </c>
       <c r="R8" s="22">
         <f>+SUM(O8:$O$60)</f>
-        <v>1356161.511816124</v>
+        <v>4104196.4007527567</v>
       </c>
       <c r="S8" s="22">
         <f>+SUM(P8:$P$60)</f>
-        <v>15990839.339348922</v>
+        <v>5006479.8703235518</v>
       </c>
       <c r="T8" s="22">
         <f>+SUM(Q8:$Q$60)</f>
-        <v>797280.53516904812</v>
+        <v>249864.65779737438</v>
       </c>
       <c r="U8" s="22">
         <f>+SUM(R8:$R$60)</f>
-        <v>26559258.620586243</v>
+        <v>67501847.380857974</v>
       </c>
       <c r="V8" s="23">
         <f>IF(A8&gt;$C$1,0,IF($C$1=55,$F$50,IF($C$1=56,$F$51,IF($C$1=60,$F$55,IF($C$1=65,$F$60,0))))/F8)</f>
-        <v>0.68173499308842878</v>
+        <v>0.32873680342949296</v>
       </c>
       <c r="W8" s="23"/>
       <c r="AA8" s="7" t="s">
@@ -3099,31 +3099,31 @@
       </c>
       <c r="P9" s="22">
         <f>+SUM(M9:$M$60)</f>
-        <v>463731.34867356677</v>
+        <v>182769.07241861126</v>
       </c>
       <c r="Q9" s="22">
         <f>+SUM(N9:$N$60)</f>
-        <v>23131.453883044742</v>
+        <v>9125.6382606970583</v>
       </c>
       <c r="R9" s="22">
         <f>+SUM(O9:$O$60)</f>
-        <v>1356161.511816124</v>
+        <v>4104196.4007527567</v>
       </c>
       <c r="S9" s="22">
         <f>+SUM(P9:$P$60)</f>
-        <v>15525494.521925721</v>
+        <v>4822097.3291553073</v>
       </c>
       <c r="T9" s="22">
         <f>+SUM(Q9:$Q$60)</f>
-        <v>774068.41551253654</v>
+        <v>240658.35376321056</v>
       </c>
       <c r="U9" s="22">
         <f>+SUM(R9:$R$60)</f>
-        <v>25203097.108770121</v>
+        <v>63397650.980105229</v>
       </c>
       <c r="V9" s="23">
         <f t="shared" ref="V9:V60" si="10">IF(A9&gt;$C$1,0,IF($C$1=55,$F$50,IF($C$1=56,$F$51,IF($C$1=60,$F$55,IF($C$1=65,$F$60,0))))/F9)</f>
-        <v>0.68187818614376261</v>
+        <v>0.32880585200080142</v>
       </c>
       <c r="W9" s="23"/>
       <c r="X9" s="14">
@@ -3264,31 +3264,31 @@
       </c>
       <c r="P10" s="22">
         <f>+SUM(M10:$M$60)</f>
-        <v>461902.22544594592</v>
+        <v>180939.94919099048</v>
       </c>
       <c r="Q10" s="22">
         <f>+SUM(N10:$N$60)</f>
-        <v>23040.007713306783</v>
+        <v>9034.192090959099</v>
       </c>
       <c r="R10" s="22">
         <f>+SUM(O10:$O$60)</f>
-        <v>1356161.511816124</v>
+        <v>4104196.4007527567</v>
       </c>
       <c r="S10" s="22">
         <f>+SUM(P10:$P$60)</f>
-        <v>15061763.173252154</v>
+        <v>4639328.2567366976</v>
       </c>
       <c r="T10" s="22">
         <f>+SUM(Q10:$Q$60)</f>
-        <v>750936.96162949188</v>
+        <v>231532.71550251354</v>
       </c>
       <c r="U10" s="22">
         <f>+SUM(R10:$R$60)</f>
-        <v>23846935.596953992</v>
+        <v>59293454.579352476</v>
       </c>
       <c r="V10" s="23">
         <f t="shared" si="10"/>
-        <v>0.68204289769955351</v>
+        <v>0.3288852769252773</v>
       </c>
       <c r="W10" s="23"/>
       <c r="X10" s="14">
@@ -3431,31 +3431,31 @@
       </c>
       <c r="P11" s="22">
         <f>+SUM(M11:$M$60)</f>
-        <v>459785.57244096458</v>
+        <v>178823.29618600913</v>
       </c>
       <c r="Q11" s="22">
         <f>+SUM(N11:$N$60)</f>
-        <v>22934.188636186729</v>
+        <v>8928.3730138390456</v>
       </c>
       <c r="R11" s="22">
         <f>+SUM(O11:$O$60)</f>
-        <v>1356161.511816124</v>
+        <v>4104196.4007527567</v>
       </c>
       <c r="S11" s="22">
         <f>+SUM(P11:$P$60)</f>
-        <v>14599860.947806207</v>
+        <v>4458388.3075457066</v>
       </c>
       <c r="T11" s="22">
         <f>+SUM(Q11:$Q$60)</f>
-        <v>727896.95391618507</v>
+        <v>222498.52341155443</v>
       </c>
       <c r="U11" s="22">
         <f>+SUM(R11:$R$60)</f>
-        <v>22490774.08513787</v>
+        <v>55189258.178599715</v>
       </c>
       <c r="V11" s="23">
         <f t="shared" si="10"/>
-        <v>0.68223630920646228</v>
+        <v>0.32897854114256442</v>
       </c>
       <c r="W11" s="23"/>
       <c r="X11" s="14">
@@ -3598,31 +3598,31 @@
       </c>
       <c r="P12" s="22">
         <f>+SUM(M12:$M$60)</f>
-        <v>457390.05064340861</v>
+        <v>176427.77438845311</v>
       </c>
       <c r="Q12" s="22">
         <f>+SUM(N12:$N$60)</f>
-        <v>22814.430183474851</v>
+        <v>8808.6145611271677</v>
       </c>
       <c r="R12" s="22">
         <f>+SUM(O12:$O$60)</f>
-        <v>1356161.511816124</v>
+        <v>4104196.4007527567</v>
       </c>
       <c r="S12" s="22">
         <f>+SUM(P12:$P$60)</f>
-        <v>14140075.375365244</v>
+        <v>4279565.0113596991</v>
       </c>
       <c r="T12" s="22">
         <f>+SUM(Q12:$Q$60)</f>
-        <v>704962.7652799983</v>
+        <v>213570.15039771536</v>
       </c>
       <c r="U12" s="22">
         <f>+SUM(R12:$R$60)</f>
-        <v>21134612.573321749</v>
+        <v>51085061.77784697</v>
       </c>
       <c r="V12" s="23">
         <f t="shared" si="10"/>
-        <v>0.68245844615147166</v>
+        <v>0.32908565694264269</v>
       </c>
       <c r="W12" s="23"/>
       <c r="X12" s="14">
@@ -3765,31 +3765,31 @@
       </c>
       <c r="P13" s="22">
         <f>+SUM(M13:$M$60)</f>
-        <v>454571.83497914061</v>
+        <v>173609.55872418519</v>
       </c>
       <c r="Q13" s="22">
         <f>+SUM(N13:$N$60)</f>
-        <v>22673.544165560685</v>
+        <v>8667.7285432130011</v>
       </c>
       <c r="R13" s="22">
         <f>+SUM(O13:$O$60)</f>
-        <v>1356161.511816124</v>
+        <v>4104196.4007527567</v>
       </c>
       <c r="S13" s="22">
         <f>+SUM(P13:$P$60)</f>
-        <v>13682685.324721836</v>
+        <v>4103137.2369712451</v>
       </c>
       <c r="T13" s="22">
         <f>+SUM(Q13:$Q$60)</f>
-        <v>682148.33509652351</v>
+        <v>204761.53583658821</v>
       </c>
       <c r="U13" s="22">
         <f>+SUM(R13:$R$60)</f>
-        <v>19778451.061505627</v>
+        <v>46980865.377094217</v>
       </c>
       <c r="V13" s="23">
         <f t="shared" si="10"/>
-        <v>0.68272367962776348</v>
+        <v>0.32921355415496512</v>
       </c>
       <c r="W13" s="23"/>
       <c r="X13" s="14">
@@ -3932,31 +3932,31 @@
       </c>
       <c r="P14" s="22">
         <f>+SUM(M14:$M$60)</f>
-        <v>451343.72996937</v>
+        <v>170381.45371441453</v>
       </c>
       <c r="Q14" s="22">
         <f>+SUM(N14:$N$60)</f>
-        <v>22512.171882448965</v>
+        <v>8506.3562601012818</v>
       </c>
       <c r="R14" s="22">
         <f>+SUM(O14:$O$60)</f>
-        <v>1356161.511816124</v>
+        <v>4104196.4007527567</v>
       </c>
       <c r="S14" s="22">
         <f>+SUM(P14:$P$60)</f>
-        <v>13228113.489742696</v>
+        <v>3929527.6782470592</v>
       </c>
       <c r="T14" s="22">
         <f>+SUM(Q14:$Q$60)</f>
-        <v>659474.79093096289</v>
+        <v>196093.80729337523</v>
       </c>
       <c r="U14" s="22">
         <f>+SUM(R14:$R$60)</f>
-        <v>18422289.549689498</v>
+        <v>42876668.976341464</v>
       </c>
       <c r="V14" s="23">
         <f t="shared" si="10"/>
-        <v>0.68303206228925573</v>
+        <v>0.3293622581695746</v>
       </c>
       <c r="W14" s="23"/>
       <c r="X14" s="14">
@@ -4052,8 +4052,8 @@
         <f t="shared" si="9"/>
         <v>2.4499999999999999E-5</v>
       </c>
-      <c r="D15" s="21">
-        <v>0.01</v>
+      <c r="D15" s="30">
+        <v>0.05</v>
       </c>
       <c r="E15" s="20">
         <f t="shared" si="3"/>
@@ -4065,15 +4065,15 @@
       </c>
       <c r="G15" s="22">
         <f t="shared" si="12"/>
-        <v>4863.7804690299699</v>
+        <v>4766.0160374916704</v>
       </c>
       <c r="H15" s="22">
         <f t="shared" si="13"/>
-        <v>243.13242051290399</v>
+        <v>238.245336683499</v>
       </c>
       <c r="I15" s="22">
         <f t="shared" si="14"/>
-        <v>99735.182910779506</v>
+        <v>498675.91455389699</v>
       </c>
       <c r="J15" s="22">
         <f t="shared" si="15"/>
@@ -4089,43 +4089,43 @@
       </c>
       <c r="M15" s="4">
         <f t="shared" si="6"/>
-        <v>3554.9984513962445</v>
+        <v>3483.5411960917904</v>
       </c>
       <c r="N15" s="22">
         <f t="shared" si="7"/>
-        <v>177.70855076852942</v>
+        <v>174.13651959730274</v>
       </c>
       <c r="O15" s="4">
         <f t="shared" si="8"/>
-        <v>72897.702323364792</v>
+        <v>364488.5116168235</v>
       </c>
       <c r="P15" s="22">
         <f>+SUM(M15:$M$60)</f>
-        <v>447866.31435286539</v>
+        <v>166904.03809791</v>
       </c>
       <c r="Q15" s="22">
         <f>+SUM(N15:$N$60)</f>
-        <v>22338.339918731657</v>
+        <v>8332.5242963839737</v>
       </c>
       <c r="R15" s="22">
         <f>+SUM(O15:$O$60)</f>
-        <v>1356161.511816124</v>
+        <v>4104196.4007527567</v>
       </c>
       <c r="S15" s="22">
         <f>+SUM(P15:$P$60)</f>
-        <v>12776769.759773327</v>
+        <v>3759146.2245326447</v>
       </c>
       <c r="T15" s="22">
         <f>+SUM(Q15:$Q$60)</f>
-        <v>636962.61904851382</v>
+        <v>187587.45103327397</v>
       </c>
       <c r="U15" s="22">
         <f>+SUM(R15:$R$60)</f>
-        <v>17066128.037873376</v>
+        <v>38772472.575588718</v>
       </c>
       <c r="V15" s="23">
         <f t="shared" si="10"/>
-        <v>0.68336929748975306</v>
+        <v>0.32952487505581241</v>
       </c>
       <c r="W15" s="23"/>
       <c r="X15" s="14">
@@ -4221,8 +4221,8 @@
         <f t="shared" si="9"/>
         <v>2.4499999999999999E-5</v>
       </c>
-      <c r="D16" s="21">
-        <v>0.01</v>
+      <c r="D16" s="30">
+        <v>0.05</v>
       </c>
       <c r="E16" s="20">
         <f t="shared" si="3"/>
@@ -4230,19 +4230,19 @@
       </c>
       <c r="F16" s="22">
         <f t="shared" si="11"/>
-        <v>9871242.5131025407</v>
+        <v>9472404.4329747912</v>
       </c>
       <c r="G16" s="22">
         <f t="shared" si="12"/>
-        <v>4812.6653313906199</v>
+        <v>4525.38578119879</v>
       </c>
       <c r="H16" s="22">
         <f t="shared" si="13"/>
-        <v>240.577258490638</v>
+        <v>226.21662423776701</v>
       </c>
       <c r="I16" s="22">
         <f t="shared" si="14"/>
-        <v>98687.031655921106</v>
+        <v>473498.38426817302</v>
       </c>
       <c r="J16" s="22">
         <f t="shared" si="15"/>
@@ -4250,7 +4250,7 @@
       </c>
       <c r="K16" s="4">
         <f t="shared" si="4"/>
-        <v>7341249.3236715542</v>
+        <v>7044633.1902814684</v>
       </c>
       <c r="L16" s="4">
         <f t="shared" si="5"/>
@@ -4258,43 +4258,43 @@
       </c>
       <c r="M16" s="4">
         <f t="shared" si="6"/>
-        <v>3468.3843359875855</v>
+        <v>3261.3481464075812</v>
       </c>
       <c r="N16" s="22">
         <f t="shared" si="7"/>
-        <v>173.37885298221249</v>
+        <v>163.029452916384</v>
       </c>
       <c r="O16" s="4">
         <f t="shared" si="8"/>
-        <v>71121.619973854409</v>
+        <v>341240.09587772988</v>
       </c>
       <c r="P16" s="22">
         <f>+SUM(M16:$M$60)</f>
-        <v>444311.31590146915</v>
+        <v>163420.49690181823</v>
       </c>
       <c r="Q16" s="22">
         <f>+SUM(N16:$N$60)</f>
-        <v>22160.631367963128</v>
+        <v>8158.3877767866716</v>
       </c>
       <c r="R16" s="22">
         <f>+SUM(O16:$O$60)</f>
-        <v>1283263.8094927592</v>
+        <v>3739707.889135933</v>
       </c>
       <c r="S16" s="22">
         <f>+SUM(P16:$P$60)</f>
-        <v>12328903.445420463</v>
+        <v>3592242.1864347351</v>
       </c>
       <c r="T16" s="22">
         <f>+SUM(Q16:$Q$60)</f>
-        <v>614624.27912978223</v>
+        <v>179254.92673688996</v>
       </c>
       <c r="U16" s="22">
         <f>+SUM(R16:$R$60)</f>
-        <v>15709966.526057255</v>
+        <v>34668276.174835972</v>
       </c>
       <c r="V16" s="23">
         <f t="shared" si="10"/>
-        <v>0.69062733711944724</v>
+        <v>0.34704684091096577</v>
       </c>
       <c r="W16" s="23"/>
       <c r="X16" s="14">
@@ -4390,8 +4390,8 @@
         <f t="shared" si="9"/>
         <v>2.4499999999999999E-5</v>
       </c>
-      <c r="D17" s="21">
-        <v>0.01</v>
+      <c r="D17" s="30">
+        <v>0.05</v>
       </c>
       <c r="E17" s="20">
         <f t="shared" si="3"/>
@@ -4399,19 +4399,19 @@
       </c>
       <c r="F17" s="22">
         <f t="shared" si="11"/>
-        <v>9767502.2388567403</v>
+        <v>8994154.4463011809</v>
       </c>
       <c r="G17" s="22">
         <f t="shared" si="12"/>
-        <v>4762.0873802695796</v>
+        <v>4296.90464899363</v>
       </c>
       <c r="H17" s="22">
         <f t="shared" si="13"/>
-        <v>238.04894954270199</v>
+        <v>214.79522660925701</v>
       </c>
       <c r="I17" s="22">
         <f t="shared" si="14"/>
-        <v>97649.895782205102</v>
+        <v>449592.03635317902</v>
       </c>
       <c r="J17" s="22">
         <f t="shared" si="15"/>
@@ -4419,7 +4419,7 @@
       </c>
       <c r="K17" s="4">
         <f t="shared" si="4"/>
-        <v>7162386.8502112823</v>
+        <v>6595300.6162297074</v>
       </c>
       <c r="L17" s="4">
         <f t="shared" si="5"/>
@@ -4427,43 +4427,43 @@
       </c>
       <c r="M17" s="4">
         <f t="shared" si="6"/>
-        <v>3383.8804901305575</v>
+        <v>3053.3273853655583</v>
       </c>
       <c r="N17" s="22">
         <f t="shared" si="7"/>
-        <v>169.15464411491376</v>
+        <v>152.63083573554474</v>
       </c>
       <c r="O17" s="4">
         <f t="shared" si="8"/>
-        <v>69388.810161223941</v>
+        <v>319474.54946689092</v>
       </c>
       <c r="P17" s="22">
         <f>+SUM(M17:$M$60)</f>
-        <v>440842.93156548165</v>
+        <v>160159.14875541063</v>
       </c>
       <c r="Q17" s="22">
         <f>+SUM(N17:$N$60)</f>
-        <v>21987.252514980915</v>
+        <v>7995.3583238702877</v>
       </c>
       <c r="R17" s="22">
         <f>+SUM(O17:$O$60)</f>
-        <v>1212142.1895189048</v>
+        <v>3398467.7932582032</v>
       </c>
       <c r="S17" s="22">
         <f>+SUM(P17:$P$60)</f>
-        <v>11884592.129518993</v>
+        <v>3428821.6895329165</v>
       </c>
       <c r="T17" s="22">
         <f>+SUM(Q17:$Q$60)</f>
-        <v>592463.64776181907</v>
+        <v>171096.53896010327</v>
       </c>
       <c r="U17" s="22">
         <f>+SUM(R17:$R$60)</f>
-        <v>14426702.716564497</v>
+        <v>30928568.285700034</v>
       </c>
       <c r="V17" s="23">
         <f t="shared" si="10"/>
-        <v>0.69796246411531304</v>
+        <v>0.36550050968346998</v>
       </c>
       <c r="W17" s="23"/>
       <c r="X17" s="14">
@@ -4559,8 +4559,8 @@
         <f t="shared" si="9"/>
         <v>2.4499999999999999E-5</v>
       </c>
-      <c r="D18" s="21">
-        <v>0.01</v>
+      <c r="D18" s="30">
+        <v>0.05</v>
       </c>
       <c r="E18" s="20">
         <f t="shared" si="3"/>
@@ -4568,19 +4568,19 @@
       </c>
       <c r="F18" s="22">
         <f t="shared" si="11"/>
-        <v>9664852.206744723</v>
+        <v>8540050.7100724</v>
       </c>
       <c r="G18" s="22">
         <f t="shared" si="12"/>
-        <v>4712.0409701893996</v>
+        <v>4079.9592466240601</v>
       </c>
       <c r="H18" s="22">
         <f t="shared" si="13"/>
-        <v>235.54721146092501</v>
+        <v>203.95048122382701</v>
       </c>
       <c r="I18" s="22">
         <f t="shared" si="14"/>
-        <v>96623.659525211799</v>
+        <v>426892.69038290298</v>
       </c>
       <c r="J18" s="22">
         <f t="shared" si="15"/>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="K18" s="4">
         <f t="shared" si="4"/>
-        <v>6987882.188753007</v>
+        <v>6174628.1237819903</v>
       </c>
       <c r="L18" s="4">
         <f t="shared" si="5"/>
@@ -4596,43 +4596,43 @@
       </c>
       <c r="M18" s="4">
         <f t="shared" si="6"/>
-        <v>3301.4354991387513</v>
+        <v>2858.5749523528984</v>
       </c>
       <c r="N18" s="22">
         <f t="shared" si="7"/>
-        <v>165.03335403065961</v>
+        <v>142.89548054411537</v>
       </c>
       <c r="O18" s="4">
         <f t="shared" si="8"/>
-        <v>67698.218591764147</v>
+        <v>299097.28953318397</v>
       </c>
       <c r="P18" s="22">
         <f>+SUM(M18:$M$60)</f>
-        <v>437459.05107535102</v>
+        <v>157105.82137004507</v>
       </c>
       <c r="Q18" s="22">
         <f>+SUM(N18:$N$60)</f>
-        <v>21818.097870866</v>
+        <v>7842.727488134743</v>
       </c>
       <c r="R18" s="22">
         <f>+SUM(O18:$O$60)</f>
-        <v>1142753.3793576809</v>
+        <v>3078993.2437913124</v>
       </c>
       <c r="S18" s="22">
         <f>+SUM(P18:$P$60)</f>
-        <v>11443749.197953513</v>
+        <v>3268662.5407775058</v>
       </c>
       <c r="T18" s="22">
         <f>+SUM(Q18:$Q$60)</f>
-        <v>570476.39524683822</v>
+        <v>163101.18063623298</v>
       </c>
       <c r="U18" s="22">
         <f>+SUM(R18:$R$60)</f>
-        <v>13214560.527045595</v>
+        <v>27530100.492441833</v>
       </c>
       <c r="V18" s="23">
         <f t="shared" si="10"/>
-        <v>0.70537549721937032</v>
+        <v>0.38493542320746477</v>
       </c>
       <c r="W18" s="23"/>
       <c r="X18" s="14">
@@ -4728,8 +4728,8 @@
         <f t="shared" si="9"/>
         <v>2.5000000000000001E-5</v>
       </c>
-      <c r="D19" s="21">
-        <v>0.01</v>
+      <c r="D19" s="30">
+        <v>0.05</v>
       </c>
       <c r="E19" s="20">
         <f t="shared" si="3"/>
@@ -4737,19 +4737,19 @@
       </c>
       <c r="F19" s="22">
         <f t="shared" si="11"/>
-        <v>9563280.9590378609</v>
+        <v>8108874.1099616494</v>
       </c>
       <c r="G19" s="22">
         <f t="shared" si="12"/>
-        <v>4757.6728054678697</v>
+        <v>3953.0267151547</v>
       </c>
       <c r="H19" s="22">
         <f t="shared" si="13"/>
-        <v>237.827142202603</v>
+        <v>197.60439297870801</v>
       </c>
       <c r="I19" s="22">
         <f t="shared" si="14"/>
-        <v>95607.706276713696</v>
+        <v>405337.27779240097</v>
       </c>
       <c r="J19" s="22">
         <f t="shared" si="15"/>
@@ -4757,7 +4757,7 @@
       </c>
       <c r="K19" s="4">
         <f t="shared" si="4"/>
-        <v>6817629.1654018983</v>
+        <v>5780787.6676885607</v>
       </c>
       <c r="L19" s="4">
         <f t="shared" si="5"/>
@@ -4765,43 +4765,43 @@
       </c>
       <c r="M19" s="4">
         <f t="shared" si="6"/>
-        <v>3286.733056872919</v>
+        <v>2730.8610975661736</v>
       </c>
       <c r="N19" s="22">
         <f t="shared" si="7"/>
-        <v>164.29762240071528</v>
+        <v>136.51062549740794</v>
       </c>
       <c r="O19" s="4">
         <f t="shared" si="8"/>
-        <v>66048.469821280465</v>
+        <v>280018.29561966984</v>
       </c>
       <c r="P19" s="22">
         <f>+SUM(M19:$M$60)</f>
-        <v>434157.61557621224</v>
+        <v>154247.24641769219</v>
       </c>
       <c r="Q19" s="22">
         <f>+SUM(N19:$N$60)</f>
-        <v>21653.06451683534</v>
+        <v>7699.8320075906277</v>
       </c>
       <c r="R19" s="22">
         <f>+SUM(O19:$O$60)</f>
-        <v>1075055.1607659163</v>
+        <v>2779895.9542581285</v>
       </c>
       <c r="S19" s="22">
         <f>+SUM(P19:$P$60)</f>
-        <v>11006290.146878162</v>
+        <v>3111556.7194074607</v>
       </c>
       <c r="T19" s="22">
         <f>+SUM(Q19:$Q$60)</f>
-        <v>548658.29737597238</v>
+        <v>155258.45314809823</v>
       </c>
       <c r="U19" s="22">
         <f>+SUM(R19:$R$60)</f>
-        <v>12071807.147687912</v>
+        <v>24451107.248650517</v>
       </c>
       <c r="V19" s="23">
         <f t="shared" si="10"/>
-        <v>0.71286726386946653</v>
+        <v>0.40540375762603581</v>
       </c>
       <c r="W19" s="23"/>
       <c r="X19" s="14">
@@ -4897,8 +4897,8 @@
         <f t="shared" si="9"/>
         <v>2.5999999999999998E-5</v>
       </c>
-      <c r="D20" s="21">
-        <v>0.01</v>
+      <c r="D20" s="30">
+        <v>0.05</v>
       </c>
       <c r="E20" s="20">
         <f t="shared" si="3"/>
@@ -4906,19 +4906,19 @@
       </c>
       <c r="F20" s="22">
         <f t="shared" si="11"/>
-        <v>9462677.7528134771</v>
+        <v>7699386.2010611156</v>
       </c>
       <c r="G20" s="22">
         <f t="shared" si="12"/>
-        <v>4895.9258214425899</v>
+        <v>3903.5380572835302</v>
       </c>
       <c r="H20" s="22">
         <f t="shared" si="13"/>
-        <v>244.73582560218401</v>
+        <v>195.12869354244799</v>
       </c>
       <c r="I20" s="22">
         <f t="shared" si="14"/>
-        <v>94600.944737708094</v>
+        <v>384864.214732608</v>
       </c>
       <c r="J20" s="22">
         <f t="shared" si="15"/>
@@ -4926,7 +4926,7 @@
       </c>
       <c r="K20" s="4">
         <f t="shared" si="4"/>
-        <v>6651454.3194355322</v>
+        <v>5412010.9488906264</v>
       </c>
       <c r="L20" s="4">
         <f t="shared" si="5"/>
@@ -4934,43 +4934,43 @@
       </c>
       <c r="M20" s="4">
         <f t="shared" si="6"/>
-        <v>3334.8844678613145</v>
+        <v>2658.9145570642354</v>
       </c>
       <c r="N20" s="22">
         <f t="shared" si="7"/>
-        <v>166.70303703446527</v>
+        <v>132.9128898315378</v>
       </c>
       <c r="O20" s="4">
         <f t="shared" si="8"/>
-        <v>64437.908734048549</v>
+        <v>262152.19322282093</v>
       </c>
       <c r="P20" s="22">
         <f>+SUM(M20:$M$60)</f>
-        <v>430870.88251933939</v>
+        <v>151516.38532012602</v>
       </c>
       <c r="Q20" s="22">
         <f>+SUM(N20:$N$60)</f>
-        <v>21488.766894434626</v>
+        <v>7563.3213820932187</v>
       </c>
       <c r="R20" s="22">
         <f>+SUM(O20:$O$60)</f>
-        <v>1009006.6909446355</v>
+        <v>2499877.6586384582</v>
       </c>
       <c r="S20" s="22">
         <f>+SUM(P20:$P$60)</f>
-        <v>10572132.531301951</v>
+        <v>2957309.4729897683</v>
       </c>
       <c r="T20" s="22">
         <f>+SUM(Q20:$Q$60)</f>
-        <v>527005.232859137</v>
+        <v>147558.6211405076</v>
       </c>
       <c r="U20" s="22">
         <f>+SUM(R20:$R$60)</f>
-        <v>10996751.986921996</v>
+        <v>21671211.294392385</v>
       </c>
       <c r="V20" s="23">
         <f t="shared" si="10"/>
-        <v>0.72044616851264209</v>
+        <v>0.42696494869186719</v>
       </c>
       <c r="W20" s="23"/>
       <c r="X20" s="14">
@@ -5066,8 +5066,8 @@
         <f t="shared" si="9"/>
         <v>2.7500000000000004E-5</v>
       </c>
-      <c r="D21" s="21">
-        <v>0.01</v>
+      <c r="D21" s="30">
+        <v>0.04</v>
       </c>
       <c r="E21" s="20">
         <f t="shared" si="3"/>
@@ -5075,19 +5075,19 @@
       </c>
       <c r="F21" s="22">
         <f t="shared" si="11"/>
-        <v>9362936.1464287248</v>
+        <v>7310423.3195776818</v>
       </c>
       <c r="G21" s="22">
         <f t="shared" si="12"/>
-        <v>5123.7963529645403</v>
+        <v>3940.2639898775401</v>
       </c>
       <c r="H21" s="22">
         <f t="shared" si="13"/>
-        <v>256.12288713807197</v>
+        <v>196.96172908779101</v>
       </c>
       <c r="I21" s="22">
         <f t="shared" si="14"/>
-        <v>93602.326340200496</v>
+        <v>292332.49849946803</v>
       </c>
       <c r="J21" s="22">
         <f t="shared" si="15"/>
@@ -5095,7 +5095,7 @@
       </c>
       <c r="K21" s="4">
         <f t="shared" si="4"/>
-        <v>6489193.5258915285</v>
+        <v>5066653.3376951804</v>
       </c>
       <c r="L21" s="4">
         <f t="shared" si="5"/>
@@ -5103,43 +5103,43 @@
       </c>
       <c r="M21" s="4">
         <f t="shared" si="6"/>
-        <v>3441.231792680489</v>
+        <v>2646.3506313390949</v>
       </c>
       <c r="N21" s="22">
         <f t="shared" si="7"/>
-        <v>172.01663792564662</v>
+        <v>132.28296313651688</v>
       </c>
       <c r="O21" s="4">
         <f t="shared" si="8"/>
-        <v>62864.969464367285</v>
+        <v>196335.65008649215</v>
       </c>
       <c r="P21" s="22">
         <f>+SUM(M21:$M$60)</f>
-        <v>427535.998051478</v>
+        <v>148857.47076306178</v>
       </c>
       <c r="Q21" s="22">
         <f>+SUM(N21:$N$60)</f>
-        <v>21322.06385740016</v>
+        <v>7430.4084922616812</v>
       </c>
       <c r="R21" s="22">
         <f>+SUM(O21:$O$60)</f>
-        <v>944568.78221058706</v>
+        <v>2237725.465415637</v>
       </c>
       <c r="S21" s="22">
         <f>+SUM(P21:$P$60)</f>
-        <v>10141261.648782611</v>
+        <v>2805793.0876696426</v>
       </c>
       <c r="T21" s="22">
         <f>+SUM(Q21:$Q$60)</f>
-        <v>505516.46596470242</v>
+        <v>139995.29975841436</v>
       </c>
       <c r="U21" s="22">
         <f>+SUM(R21:$R$60)</f>
-        <v>9987745.2959773615</v>
+        <v>19171333.635753926</v>
       </c>
       <c r="V21" s="23">
         <f t="shared" si="10"/>
-        <v>0.72812094670586935</v>
+        <v>0.44968230847743007</v>
       </c>
       <c r="W21" s="23"/>
       <c r="X21" s="14">
@@ -5235,8 +5235,8 @@
         <f t="shared" si="9"/>
         <v>2.9999999999999997E-5</v>
       </c>
-      <c r="D22" s="21">
-        <v>0.01</v>
+      <c r="D22" s="30">
+        <v>0.04</v>
       </c>
       <c r="E22" s="20">
         <f t="shared" si="3"/>
@@ -5244,19 +5244,19 @@
       </c>
       <c r="F22" s="22">
         <f t="shared" si="11"/>
-        <v>9263953.9008484222</v>
+        <v>7013953.5953592481</v>
       </c>
       <c r="G22" s="22">
         <f t="shared" si="12"/>
-        <v>5530.4975200993304</v>
+        <v>4124.1428510005298</v>
       </c>
       <c r="H22" s="22">
         <f t="shared" si="13"/>
-        <v>276.44606523314297</v>
+        <v>206.14837263285099</v>
       </c>
       <c r="I22" s="22">
         <f t="shared" si="14"/>
-        <v>92610.357970574507</v>
+        <v>280469.76926158002</v>
       </c>
       <c r="J22" s="22">
         <f t="shared" si="15"/>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="K22" s="4">
         <f t="shared" si="4"/>
-        <v>6330691.5275922706</v>
+        <v>4793112.8626406007</v>
       </c>
       <c r="L22" s="4">
         <f t="shared" si="5"/>
@@ -5272,43 +5272,43 @@
       </c>
       <c r="M22" s="4">
         <f t="shared" si="6"/>
-        <v>3662.3712894175719</v>
+        <v>2731.0639442597189</v>
       </c>
       <c r="N22" s="22">
         <f t="shared" si="7"/>
-        <v>183.06637489716044</v>
+        <v>136.51427896800661</v>
       </c>
       <c r="O22" s="4">
         <f t="shared" si="8"/>
-        <v>61327.848878236931</v>
+        <v>185730.92687594824</v>
       </c>
       <c r="P22" s="22">
         <f>+SUM(M22:$M$60)</f>
-        <v>424094.76625879755</v>
+        <v>146211.12013172268</v>
       </c>
       <c r="Q22" s="22">
         <f>+SUM(N22:$N$60)</f>
-        <v>21150.047219474516</v>
+        <v>7298.1255291251646</v>
       </c>
       <c r="R22" s="22">
         <f>+SUM(O22:$O$60)</f>
-        <v>881703.8127462198</v>
+        <v>2041389.8153291449</v>
       </c>
       <c r="S22" s="22">
         <f>+SUM(P22:$P$60)</f>
-        <v>9713725.6507311314</v>
+        <v>2656935.6169065805</v>
       </c>
       <c r="T22" s="22">
         <f>+SUM(Q22:$Q$60)</f>
-        <v>484194.40210730222</v>
+        <v>132564.89126615273</v>
       </c>
       <c r="U22" s="22">
         <f>+SUM(R22:$R$60)</f>
-        <v>9043176.5137667749</v>
+        <v>16933608.170338295</v>
       </c>
       <c r="V22" s="23">
         <f t="shared" si="10"/>
-        <v>0.73590067522463953</v>
+        <v>0.46868973248839313</v>
       </c>
       <c r="W22" s="23"/>
       <c r="X22" s="14">
@@ -5404,8 +5404,8 @@
         <f t="shared" si="9"/>
         <v>3.2499999999999997E-5</v>
       </c>
-      <c r="D23" s="21">
-        <v>0.01</v>
+      <c r="D23" s="30">
+        <v>0.04</v>
       </c>
       <c r="E23" s="20">
         <f t="shared" si="3"/>
@@ -5413,19 +5413,19 @@
       </c>
       <c r="F23" s="22">
         <f t="shared" si="11"/>
-        <v>9165536.5992925148</v>
+        <v>6729153.534874035</v>
       </c>
       <c r="G23" s="22">
         <f t="shared" si="12"/>
-        <v>5927.7144686669999</v>
+        <v>4286.4011465642297</v>
       </c>
       <c r="H23" s="22">
         <f t="shared" si="13"/>
-        <v>296.29421285419301</v>
+        <v>214.25388493521001</v>
       </c>
       <c r="I23" s="22">
         <f t="shared" si="14"/>
-        <v>91624.089083334999</v>
+        <v>269074.28987074399</v>
       </c>
       <c r="J23" s="22">
         <f t="shared" si="15"/>
@@ -5433,7 +5433,7 @@
       </c>
       <c r="K23" s="4">
         <f t="shared" si="4"/>
-        <v>6175736.6120361099</v>
+        <v>4534102.2211990943</v>
       </c>
       <c r="L23" s="4">
         <f t="shared" si="5"/>
@@ -5441,43 +5441,43 @@
       </c>
       <c r="M23" s="4">
         <f t="shared" si="6"/>
-        <v>3870.450765384825</v>
+        <v>2798.7691860260393</v>
       </c>
       <c r="N23" s="22">
         <f t="shared" si="7"/>
-        <v>193.46278721459598</v>
+        <v>139.89525259988378</v>
       </c>
       <c r="O23" s="4">
         <f t="shared" si="8"/>
-        <v>59825.169986642133</v>
+        <v>175689.76992405538</v>
       </c>
       <c r="P23" s="22">
         <f>+SUM(M23:$M$60)</f>
-        <v>420432.39496937994</v>
+        <v>143480.05618746296</v>
       </c>
       <c r="Q23" s="22">
         <f>+SUM(N23:$N$60)</f>
-        <v>20966.980844577352</v>
+        <v>7161.6112501571597</v>
       </c>
       <c r="R23" s="22">
         <f>+SUM(O23:$O$60)</f>
-        <v>820375.96386798285</v>
+        <v>1855658.8884531965</v>
       </c>
       <c r="S23" s="22">
         <f>+SUM(P23:$P$60)</f>
-        <v>9289630.8844723348</v>
+        <v>2510724.4967748574</v>
       </c>
       <c r="T23" s="22">
         <f>+SUM(Q23:$Q$60)</f>
-        <v>463044.35488782765</v>
+        <v>125266.76573702754</v>
       </c>
       <c r="U23" s="22">
         <f>+SUM(R23:$R$60)</f>
-        <v>8161472.7010205528</v>
+        <v>14892218.355009144</v>
       </c>
       <c r="V23" s="23">
         <f t="shared" si="10"/>
-        <v>0.74380259759265122</v>
+        <v>0.48852623398441547</v>
       </c>
       <c r="W23" s="23"/>
       <c r="X23" s="14">
@@ -5573,8 +5573,8 @@
         <f t="shared" si="9"/>
         <v>3.5000000000000004E-5</v>
       </c>
-      <c r="D24" s="21">
-        <v>0.01</v>
+      <c r="D24" s="30">
+        <v>0.04</v>
       </c>
       <c r="E24" s="20">
         <f t="shared" si="3"/>
@@ -5582,19 +5582,19 @@
       </c>
       <c r="F24" s="22">
         <f t="shared" si="11"/>
-        <v>9067688.5015276596</v>
+        <v>6455578.589971792</v>
       </c>
       <c r="G24" s="22">
         <f t="shared" si="12"/>
-        <v>6315.5345175257899</v>
+        <v>4428.4494134996803</v>
       </c>
       <c r="H24" s="22">
         <f t="shared" si="13"/>
-        <v>315.671728277478</v>
+        <v>221.34884641506</v>
       </c>
       <c r="I24" s="22">
         <f t="shared" si="14"/>
-        <v>90643.561815429406</v>
+        <v>258128.24817521599</v>
       </c>
       <c r="J24" s="22">
         <f t="shared" si="15"/>
@@ -5602,7 +5602,7 @@
       </c>
       <c r="K24" s="4">
         <f t="shared" si="4"/>
-        <v>6024258.0225100275</v>
+        <v>4288862.7133618034</v>
       </c>
       <c r="L24" s="4">
         <f t="shared" si="5"/>
@@ -5610,43 +5610,43 @@
       </c>
       <c r="M24" s="4">
         <f t="shared" si="6"/>
-        <v>4065.9355187646534</v>
+        <v>2851.0318031568449</v>
       </c>
       <c r="N24" s="22">
         <f t="shared" si="7"/>
-        <v>203.22917857727964</v>
+        <v>142.50419092462818</v>
       </c>
       <c r="O24" s="4">
         <f t="shared" si="8"/>
-        <v>58356.24467097038</v>
+        <v>166182.73714435799</v>
       </c>
       <c r="P24" s="22">
         <f>+SUM(M24:$M$60)</f>
-        <v>416561.94420399511</v>
+        <v>140681.28700143693</v>
       </c>
       <c r="Q24" s="22">
         <f>+SUM(N24:$N$60)</f>
-        <v>20773.518057362759</v>
+        <v>7021.7159975572749</v>
       </c>
       <c r="R24" s="22">
         <f>+SUM(O24:$O$60)</f>
-        <v>760550.79388134077</v>
+        <v>1679969.1185291416</v>
       </c>
       <c r="S24" s="22">
         <f>+SUM(P24:$P$60)</f>
-        <v>8869198.4895029552</v>
+        <v>2367244.4405873944</v>
       </c>
       <c r="T24" s="22">
         <f>+SUM(Q24:$Q$60)</f>
-        <v>442077.37404325034</v>
+        <v>118105.15448687036</v>
       </c>
       <c r="U24" s="22">
         <f>+SUM(R24:$R$60)</f>
-        <v>7341096.7371525699</v>
+        <v>13036559.466555947</v>
       </c>
       <c r="V24" s="23">
         <f t="shared" si="10"/>
-        <v>0.75182886242020219</v>
+        <v>0.50922903167836642</v>
       </c>
       <c r="W24" s="23"/>
       <c r="X24" s="14">
@@ -5742,8 +5742,8 @@
         <f t="shared" si="9"/>
         <v>3.7500000000000003E-5</v>
       </c>
-      <c r="D25" s="21">
-        <v>0.01</v>
+      <c r="D25" s="30">
+        <v>0.04</v>
       </c>
       <c r="E25" s="20">
         <f t="shared" si="3"/>
@@ -5751,19 +5751,19 @@
       </c>
       <c r="F25" s="22">
         <f t="shared" si="11"/>
-        <v>8970413.7334664259</v>
+        <v>6192800.5435366612</v>
       </c>
       <c r="G25" s="22">
         <f t="shared" si="12"/>
-        <v>6694.0457328884104</v>
+        <v>4551.6230549669599</v>
       </c>
       <c r="H25" s="22">
         <f t="shared" si="13"/>
-        <v>334.58304671905501</v>
+        <v>227.500075442482</v>
       </c>
       <c r="I25" s="22">
         <f t="shared" si="14"/>
-        <v>89668.816961321005</v>
+        <v>247614.48687463099</v>
       </c>
       <c r="J25" s="22">
         <f t="shared" si="15"/>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="K25" s="4">
         <f t="shared" si="4"/>
-        <v>5876186.1960329646</v>
+        <v>4056674.5470114909</v>
       </c>
       <c r="L25" s="4">
         <f t="shared" si="5"/>
@@ -5779,43 +5779,43 @@
       </c>
       <c r="M25" s="4">
         <f t="shared" si="6"/>
-        <v>4249.2780641945028</v>
+        <v>2889.3008467104664</v>
       </c>
       <c r="N25" s="22">
         <f t="shared" si="7"/>
-        <v>212.38821152498767</v>
+        <v>144.41357569919194</v>
       </c>
       <c r="O25" s="4">
         <f t="shared" si="8"/>
-        <v>56920.396447844978</v>
+        <v>157181.89708260947</v>
       </c>
       <c r="P25" s="22">
         <f>+SUM(M25:$M$60)</f>
-        <v>412496.00868523045</v>
+        <v>137830.25519828007</v>
       </c>
       <c r="Q25" s="22">
         <f>+SUM(N25:$N$60)</f>
-        <v>20570.288878785479</v>
+        <v>6879.2118066326466</v>
       </c>
       <c r="R25" s="22">
         <f>+SUM(O25:$O$60)</f>
-        <v>702194.5492103704</v>
+        <v>1513786.3813847832</v>
       </c>
       <c r="S25" s="22">
         <f>+SUM(P25:$P$60)</f>
-        <v>8452636.5452989601</v>
+        <v>2226563.1535859574</v>
       </c>
       <c r="T25" s="22">
         <f>+SUM(Q25:$Q$60)</f>
-        <v>421303.85598588758</v>
+        <v>111083.43848931309</v>
       </c>
       <c r="U25" s="22">
         <f>+SUM(R25:$R$60)</f>
-        <v>6580545.9432712281</v>
+        <v>11356590.348026806</v>
       </c>
       <c r="V25" s="23">
         <f t="shared" si="10"/>
-        <v>0.7599816612081578</v>
+        <v>0.53083706009648723</v>
       </c>
       <c r="W25" s="23"/>
       <c r="X25" s="14">
@@ -5911,8 +5911,8 @@
         <f t="shared" si="9"/>
         <v>4.0500000000000002E-5</v>
       </c>
-      <c r="D26" s="26">
-        <v>8.9999999999999993E-3</v>
+      <c r="D26" s="30">
+        <v>0.04</v>
       </c>
       <c r="E26" s="20">
         <f t="shared" si="3"/>
@@ -5920,19 +5920,19 @@
       </c>
       <c r="F26" s="22">
         <f t="shared" si="11"/>
-        <v>8873716.287725497</v>
+        <v>5940406.9335316205</v>
       </c>
       <c r="G26" s="22">
         <f t="shared" si="12"/>
-        <v>7155.2206010375703</v>
+        <v>4715.3995350631703</v>
       </c>
       <c r="H26" s="22">
         <f t="shared" si="13"/>
-        <v>357.62337870812701</v>
+        <v>235.67926241763701</v>
       </c>
       <c r="I26" s="22">
         <f t="shared" si="14"/>
-        <v>79829.485313847399</v>
+        <v>237515.23296807599</v>
       </c>
       <c r="J26" s="22">
         <f t="shared" si="15"/>
@@ -5940,7 +5940,7 @@
       </c>
       <c r="K26" s="4">
         <f t="shared" si="4"/>
-        <v>5731452.7484621713</v>
+        <v>3836854.8804370761</v>
       </c>
       <c r="L26" s="4">
         <f t="shared" si="5"/>
@@ -5948,43 +5948,43 @@
       </c>
       <c r="M26" s="4">
         <f t="shared" si="6"/>
-        <v>4478.4281062133796</v>
+        <v>2951.3524442265511</v>
       </c>
       <c r="N26" s="22">
         <f t="shared" si="7"/>
-        <v>223.83524980532718</v>
+        <v>147.51084441893119</v>
       </c>
       <c r="O26" s="4">
         <f t="shared" si="8"/>
-        <v>49965.001873211324</v>
+        <v>148659.97210817024</v>
       </c>
       <c r="P26" s="22">
         <f>+SUM(M26:$M$60)</f>
-        <v>408246.73062103597</v>
+        <v>134940.95435156961</v>
       </c>
       <c r="Q26" s="22">
         <f>+SUM(N26:$N$60)</f>
-        <v>20357.900667260492</v>
+        <v>6734.7982309334557</v>
       </c>
       <c r="R26" s="22">
         <f>+SUM(O26:$O$60)</f>
-        <v>645274.15276252537</v>
+        <v>1356604.4843021741</v>
       </c>
       <c r="S26" s="22">
         <f>+SUM(P26:$P$60)</f>
-        <v>8040140.5366137289</v>
+        <v>2088732.898387678</v>
       </c>
       <c r="T26" s="22">
         <f>+SUM(Q26:$Q$60)</f>
-        <v>400733.56710710214</v>
+        <v>104204.22668268043</v>
       </c>
       <c r="U26" s="22">
         <f>+SUM(R26:$R$60)</f>
-        <v>5878351.3940608585</v>
+        <v>9842803.966642024</v>
       </c>
       <c r="V26" s="23">
         <f t="shared" si="10"/>
-        <v>0.76826322927569102</v>
+        <v>0.55339105065998606</v>
       </c>
       <c r="W26" s="23"/>
       <c r="X26" s="14">
@@ -6080,8 +6080,8 @@
         <f t="shared" si="9"/>
         <v>4.35E-5</v>
       </c>
-      <c r="D27" s="26">
-        <v>8.9999999999999993E-3</v>
+      <c r="D27" s="30">
+        <v>0.04</v>
       </c>
       <c r="E27" s="20">
         <f t="shared" si="3"/>
@@ -6089,19 +6089,19 @@
       </c>
       <c r="F27" s="22">
         <f t="shared" si="11"/>
-        <v>8786373.9584319033</v>
+        <v>5697940.6217660643</v>
       </c>
       <c r="G27" s="22">
         <f t="shared" si="12"/>
-        <v>7609.5811777979898</v>
+        <v>4857.9585112219602</v>
       </c>
       <c r="H27" s="22">
         <f t="shared" si="13"/>
-        <v>380.32182249892202</v>
+        <v>242.79754581009999</v>
       </c>
       <c r="I27" s="22">
         <f t="shared" si="14"/>
-        <v>79041.247787308195</v>
+        <v>227813.52565186899</v>
       </c>
       <c r="J27" s="22">
         <f t="shared" si="15"/>
@@ -6109,7 +6109,7 @@
       </c>
       <c r="K27" s="4">
         <f t="shared" si="4"/>
-        <v>5595578.1155629568</v>
+        <v>3628717.8303325437</v>
       </c>
       <c r="L27" s="4">
         <f t="shared" si="5"/>
@@ -6117,43 +6117,43 @@
       </c>
       <c r="M27" s="4">
         <f t="shared" si="6"/>
-        <v>4696.1227004890952</v>
+        <v>2998.0058967168147</v>
       </c>
       <c r="N27" s="22">
         <f t="shared" si="7"/>
-        <v>234.70909927862866</v>
+        <v>149.83834719163838</v>
       </c>
       <c r="O27" s="4">
         <f t="shared" si="8"/>
-        <v>48778.952393852145</v>
+        <v>140591.21577066614</v>
       </c>
       <c r="P27" s="22">
         <f>+SUM(M27:$M$60)</f>
-        <v>403768.30251482263</v>
+        <v>131989.60190734305</v>
       </c>
       <c r="Q27" s="22">
         <f>+SUM(N27:$N$60)</f>
-        <v>20134.065417455164</v>
+        <v>6587.2873865145239</v>
       </c>
       <c r="R27" s="22">
         <f>+SUM(O27:$O$60)</f>
-        <v>595309.15088931401</v>
+        <v>1207944.5121940037</v>
       </c>
       <c r="S27" s="22">
         <f>+SUM(P27:$P$60)</f>
-        <v>7631893.8059926927</v>
+        <v>1953791.9440361082</v>
       </c>
       <c r="T27" s="22">
         <f>+SUM(Q27:$Q$60)</f>
-        <v>380375.66643984162</v>
+        <v>97469.428451746979</v>
       </c>
       <c r="U27" s="22">
         <f>+SUM(R27:$R$60)</f>
-        <v>5233077.2412983328</v>
+        <v>8486199.4823398441</v>
       </c>
       <c r="V27" s="23">
         <f t="shared" si="10"/>
-        <v>0.77590027047983445</v>
+        <v>0.57693967917763533</v>
       </c>
       <c r="W27" s="23"/>
       <c r="X27" s="14">
@@ -6249,8 +6249,8 @@
         <f t="shared" si="9"/>
         <v>4.6500000000000005E-5</v>
       </c>
-      <c r="D28" s="26">
-        <v>8.9999999999999993E-3</v>
+      <c r="D28" s="30">
+        <v>0.04</v>
       </c>
       <c r="E28" s="20">
         <f t="shared" si="3"/>
@@ -6258,19 +6258,19 @@
       </c>
       <c r="F28" s="22">
         <f t="shared" si="11"/>
-        <v>8699342.8076443002</v>
+        <v>5465026.3400571626</v>
       </c>
       <c r="G28" s="22">
         <f t="shared" si="12"/>
-        <v>8053.7948063762797</v>
+        <v>4980.7092021466997</v>
       </c>
       <c r="H28" s="22">
         <f t="shared" si="13"/>
-        <v>402.51184799003101</v>
+        <v>248.925446135008</v>
       </c>
       <c r="I28" s="22">
         <f t="shared" si="14"/>
-        <v>78255.859028123101</v>
+        <v>218494.32400121601</v>
       </c>
       <c r="J28" s="22">
         <f t="shared" si="15"/>
@@ -6278,7 +6278,7 @@
       </c>
       <c r="K28" s="4">
         <f t="shared" si="4"/>
-        <v>5462580.2112542726</v>
+        <v>3431655.1720374809</v>
       </c>
       <c r="L28" s="4">
         <f t="shared" si="5"/>
@@ -6286,43 +6286,43 @@
       </c>
       <c r="M28" s="4">
         <f t="shared" si="6"/>
-        <v>4900.6687042753038</v>
+        <v>3030.7210822818106</v>
       </c>
       <c r="N28" s="22">
         <f t="shared" si="7"/>
-        <v>244.92518917703885</v>
+        <v>151.46911150577017</v>
       </c>
       <c r="O28" s="4">
         <f t="shared" si="8"/>
-        <v>47618.054406064177</v>
+        <v>132952.02093388425</v>
       </c>
       <c r="P28" s="22">
         <f>+SUM(M28:$M$60)</f>
-        <v>399072.1798143335</v>
+        <v>128991.59601062622</v>
       </c>
       <c r="Q28" s="22">
         <f>+SUM(N28:$N$60)</f>
-        <v>19899.356318176538</v>
+        <v>6437.4490393228853</v>
       </c>
       <c r="R28" s="22">
         <f>+SUM(O28:$O$60)</f>
-        <v>546530.19849546195</v>
+        <v>1067353.2964233372</v>
       </c>
       <c r="S28" s="22">
         <f>+SUM(P28:$P$60)</f>
-        <v>7228125.5034778696</v>
+        <v>1821802.3421287653</v>
       </c>
       <c r="T28" s="22">
         <f>+SUM(Q28:$Q$60)</f>
-        <v>360241.60102238646</v>
+        <v>90882.141065232456</v>
       </c>
       <c r="U28" s="22">
         <f>+SUM(R28:$R$60)</f>
-        <v>4637768.09040902</v>
+        <v>7278254.9701458411</v>
       </c>
       <c r="V28" s="23">
         <f t="shared" si="10"/>
-        <v>0.78366263769876221</v>
+        <v>0.6015283055818802</v>
       </c>
       <c r="W28" s="23"/>
       <c r="X28" s="14">
@@ -6418,8 +6418,8 @@
         <f t="shared" si="9"/>
         <v>4.9500000000000004E-5</v>
       </c>
-      <c r="D29" s="26">
-        <v>8.9999999999999993E-3</v>
+      <c r="D29" s="30">
+        <v>0.04</v>
       </c>
       <c r="E29" s="20">
         <f t="shared" si="3"/>
@@ -6427,19 +6427,19 @@
       </c>
       <c r="F29" s="22">
         <f t="shared" si="11"/>
-        <v>8612630.6419618111</v>
+        <v>5241302.3814076642</v>
       </c>
       <c r="G29" s="22">
         <f t="shared" si="12"/>
-        <v>8487.9249846893708</v>
+        <v>5084.9857139303504</v>
       </c>
       <c r="H29" s="22">
         <f t="shared" si="13"/>
-        <v>424.19667195872802</v>
+        <v>254.12972201071699</v>
       </c>
       <c r="I29" s="22">
         <f t="shared" si="14"/>
-        <v>77473.388994310299</v>
+        <v>209543.13114829699</v>
       </c>
       <c r="J29" s="22">
         <f t="shared" si="15"/>
@@ -6447,7 +6447,7 @@
       </c>
       <c r="K29" s="4">
         <f t="shared" si="4"/>
-        <v>5332407.2123937244</v>
+        <v>3245089.6575994785</v>
       </c>
       <c r="L29" s="4">
         <f t="shared" si="5"/>
@@ -6455,43 +6455,43 @@
       </c>
       <c r="M29" s="4">
         <f t="shared" si="6"/>
-        <v>5092.5161962777038</v>
+        <v>3050.8483702131512</v>
       </c>
       <c r="N29" s="22">
         <f t="shared" si="7"/>
-        <v>254.50606906323637</v>
+        <v>152.47068366291512</v>
       </c>
       <c r="O29" s="4">
         <f t="shared" si="8"/>
-        <v>46481.853803575599</v>
+        <v>125719.98351968206</v>
       </c>
       <c r="P29" s="22">
         <f>+SUM(M29:$M$60)</f>
-        <v>394171.51111005823</v>
+        <v>125960.8749283444</v>
       </c>
       <c r="Q29" s="22">
         <f>+SUM(N29:$N$60)</f>
-        <v>19654.431128999498</v>
+        <v>6285.9799278171149</v>
       </c>
       <c r="R29" s="22">
         <f>+SUM(O29:$O$60)</f>
-        <v>498912.1440893978</v>
+        <v>934401.27548945299</v>
       </c>
       <c r="S29" s="22">
         <f>+SUM(P29:$P$60)</f>
-        <v>6829053.3236635365</v>
+        <v>1692810.746118139</v>
       </c>
       <c r="T29" s="22">
         <f>+SUM(Q29:$Q$60)</f>
-        <v>340342.24470420991</v>
+        <v>84444.692025909579</v>
       </c>
       <c r="U29" s="22">
         <f>+SUM(R29:$R$60)</f>
-        <v>4091237.8919135593</v>
+        <v>6210901.6737225037</v>
       </c>
       <c r="V29" s="23">
         <f t="shared" si="10"/>
-        <v>0.79155257136760382</v>
+        <v>0.62720442269389465</v>
       </c>
       <c r="W29" s="23"/>
       <c r="X29" s="14">
@@ -6587,8 +6587,8 @@
         <f t="shared" si="9"/>
         <v>5.3499999999999999E-5</v>
       </c>
-      <c r="D30" s="26">
-        <v>8.9999999999999993E-3</v>
+      <c r="D30" s="30">
+        <v>0.03</v>
       </c>
       <c r="E30" s="20">
         <f t="shared" si="3"/>
@@ -6596,19 +6596,19 @@
       </c>
       <c r="F30" s="22">
         <f t="shared" si="11"/>
-        <v>8526245.1313108522</v>
+        <v>5026420.1348234257</v>
       </c>
       <c r="G30" s="22">
         <f t="shared" si="12"/>
-        <v>9081.7854759351103</v>
+        <v>5297.4537904175004</v>
       </c>
       <c r="H30" s="22">
         <f t="shared" si="13"/>
-        <v>453.85847674952697</v>
+        <v>264.73806437520301</v>
       </c>
       <c r="I30" s="22">
         <f t="shared" si="14"/>
-        <v>76693.100716166096</v>
+        <v>150707.89845741101</v>
       </c>
       <c r="J30" s="22">
         <f t="shared" si="15"/>
@@ -6616,7 +6616,7 @@
       </c>
       <c r="K30" s="4">
         <f t="shared" si="4"/>
-        <v>5205008.0026124464</v>
+        <v>3068473.4749381933</v>
       </c>
       <c r="L30" s="4">
         <f t="shared" si="5"/>
@@ -6624,43 +6624,43 @@
       </c>
       <c r="M30" s="4">
         <f t="shared" si="6"/>
-        <v>5372.522312077529</v>
+        <v>3133.8208507162776</v>
       </c>
       <c r="N30" s="22">
         <f t="shared" si="7"/>
-        <v>268.4895827283662</v>
+        <v>156.61140218306539</v>
       </c>
       <c r="O30" s="4">
         <f t="shared" si="8"/>
-        <v>45369.426075062198</v>
+        <v>89154.445369167457</v>
       </c>
       <c r="P30" s="22">
         <f>+SUM(M30:$M$60)</f>
-        <v>389078.99491378054</v>
+        <v>122910.02655813126</v>
       </c>
       <c r="Q30" s="22">
         <f>+SUM(N30:$N$60)</f>
-        <v>19399.92505993626</v>
+        <v>6133.509244154201</v>
       </c>
       <c r="R30" s="22">
         <f>+SUM(O30:$O$60)</f>
-        <v>452430.29028582218</v>
+        <v>808681.29196977091</v>
       </c>
       <c r="S30" s="22">
         <f>+SUM(P30:$P$60)</f>
-        <v>6434881.8125534784</v>
+        <v>1566849.8711897945</v>
       </c>
       <c r="T30" s="22">
         <f>+SUM(Q30:$Q$60)</f>
-        <v>320687.8135752104</v>
+        <v>78158.712098092452</v>
       </c>
       <c r="U30" s="22">
         <f>+SUM(R30:$R$60)</f>
-        <v>3592325.7478241613</v>
+        <v>5276500.3982330514</v>
       </c>
       <c r="V30" s="23">
         <f t="shared" si="10"/>
-        <v>0.79957235874546884</v>
+        <v>0.65401775938302298</v>
       </c>
       <c r="W30" s="23"/>
       <c r="X30" s="14">
@@ -6756,8 +6756,8 @@
         <f t="shared" si="9"/>
         <v>5.8E-5</v>
       </c>
-      <c r="D31" s="26">
-        <v>7.0000000000000001E-3</v>
+      <c r="D31" s="30">
+        <v>0.03</v>
       </c>
       <c r="E31" s="20">
         <f t="shared" si="3"/>
@@ -6765,19 +6765,19 @@
       </c>
       <c r="F31" s="22">
         <f t="shared" si="11"/>
-        <v>8440016.3866420016</v>
+        <v>4870150.0445112223</v>
       </c>
       <c r="G31" s="22">
         <f t="shared" si="12"/>
-        <v>9755.86961355124</v>
+        <v>5564.47206648874</v>
       </c>
       <c r="H31" s="22">
         <f t="shared" si="13"/>
-        <v>487.524698675031</v>
+        <v>278.070297673141</v>
       </c>
       <c r="I31" s="22">
         <f t="shared" si="14"/>
-        <v>59044.135910365301</v>
+        <v>146015.52615150099</v>
       </c>
       <c r="J31" s="22">
         <f t="shared" si="15"/>
@@ -6785,7 +6785,7 @@
       </c>
       <c r="K31" s="4">
         <f t="shared" si="4"/>
-        <v>5080225.3742360836</v>
+        <v>2931446.8952478771</v>
       </c>
       <c r="L31" s="4">
         <f t="shared" si="5"/>
@@ -6793,43 +6793,43 @@
       </c>
       <c r="M31" s="4">
         <f t="shared" si="6"/>
-        <v>5690.4823230259653</v>
+        <v>3245.690152248736</v>
       </c>
       <c r="N31" s="22">
         <f t="shared" si="7"/>
-        <v>284.36733881675644</v>
+        <v>162.1950862555228</v>
       </c>
       <c r="O31" s="4">
         <f t="shared" si="8"/>
-        <v>34439.739867943208</v>
+        <v>85169.113914591988</v>
       </c>
       <c r="P31" s="22">
         <f>+SUM(M31:$M$60)</f>
-        <v>383706.47260170296</v>
+        <v>119776.20570741498</v>
       </c>
       <c r="Q31" s="22">
         <f>+SUM(N31:$N$60)</f>
-        <v>19131.435477207895</v>
+        <v>5976.8978419711357</v>
       </c>
       <c r="R31" s="22">
         <f>+SUM(O31:$O$60)</f>
-        <v>407060.86421075993</v>
+        <v>719526.84660060343</v>
       </c>
       <c r="S31" s="22">
         <f>+SUM(P31:$P$60)</f>
-        <v>6045802.8176396992</v>
+        <v>1443939.8446316635</v>
       </c>
       <c r="T31" s="22">
         <f>+SUM(Q31:$Q$60)</f>
-        <v>301287.88851527416</v>
+        <v>72025.202853938259</v>
       </c>
       <c r="U31" s="22">
         <f>+SUM(R31:$R$60)</f>
-        <v>3139895.4575383388</v>
+        <v>4467819.1062632808</v>
       </c>
       <c r="V31" s="23">
         <f t="shared" si="10"/>
-        <v>0.80774131453987397</v>
+        <v>0.67500344019171921</v>
       </c>
       <c r="W31" s="23"/>
       <c r="X31" s="14">
@@ -6925,8 +6925,8 @@
         <f t="shared" si="9"/>
         <v>6.3500000000000012E-5</v>
       </c>
-      <c r="D32" s="26">
-        <v>7.0000000000000001E-3</v>
+      <c r="D32" s="30">
+        <v>0.03</v>
       </c>
       <c r="E32" s="20">
         <f t="shared" si="3"/>
@@ -6934,19 +6934,19 @@
       </c>
       <c r="F32" s="22">
         <f t="shared" si="11"/>
-        <v>8370728.8564194106</v>
+        <v>4718291.9759955592</v>
       </c>
       <c r="G32" s="22">
         <f t="shared" si="12"/>
-        <v>10593.2814105221</v>
+        <v>5902.15994784337</v>
       </c>
       <c r="H32" s="22">
         <f t="shared" si="13"/>
-        <v>529.34454053048103</v>
+        <v>294.92996784030299</v>
       </c>
       <c r="I32" s="22">
         <f t="shared" si="14"/>
-        <v>58556.034892031203</v>
+        <v>141454.384498417</v>
       </c>
       <c r="J32" s="22">
         <f t="shared" si="15"/>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="K32" s="4">
         <f t="shared" si="4"/>
-        <v>4967971.1659860546</v>
+        <v>2800274.4912079182</v>
       </c>
       <c r="L32" s="4">
         <f t="shared" si="5"/>
@@ -6962,43 +6962,43 @@
       </c>
       <c r="M32" s="4">
         <f t="shared" si="6"/>
-        <v>6092.4181486560719</v>
+        <v>3394.455880950648</v>
       </c>
       <c r="N32" s="22">
         <f t="shared" si="7"/>
-        <v>304.43713903574712</v>
+        <v>169.62040552118731</v>
       </c>
       <c r="O32" s="4">
         <f t="shared" si="8"/>
-        <v>33676.802858762763</v>
+        <v>81353.381065580063</v>
       </c>
       <c r="P32" s="22">
         <f>+SUM(M32:$M$60)</f>
-        <v>378015.99027867703</v>
+        <v>116530.51555516623</v>
       </c>
       <c r="Q32" s="22">
         <f>+SUM(N32:$N$60)</f>
-        <v>18847.06813839114</v>
+        <v>5814.7027557156125</v>
       </c>
       <c r="R32" s="22">
         <f>+SUM(O32:$O$60)</f>
-        <v>372621.12434281677</v>
+        <v>634357.73268601147</v>
       </c>
       <c r="S32" s="22">
         <f>+SUM(P32:$P$60)</f>
-        <v>5662096.3450379968</v>
+        <v>1324163.6389242483</v>
       </c>
       <c r="T32" s="22">
         <f>+SUM(Q32:$Q$60)</f>
-        <v>282156.45303806622</v>
+        <v>66048.305011967124</v>
       </c>
       <c r="U32" s="22">
         <f>+SUM(R32:$R$60)</f>
-        <v>2732834.5933275786</v>
+        <v>3748292.259662678</v>
       </c>
       <c r="V32" s="23">
         <f t="shared" si="10"/>
-        <v>0.81442727960972539</v>
+        <v>0.69672840320597051</v>
       </c>
       <c r="W32" s="23"/>
       <c r="X32" s="14">
@@ -7094,8 +7094,8 @@
         <f t="shared" si="9"/>
         <v>6.9499999999999995E-5</v>
       </c>
-      <c r="D33" s="26">
-        <v>7.0000000000000001E-3</v>
+      <c r="D33" s="30">
+        <v>0.03</v>
       </c>
       <c r="E33" s="20">
         <f t="shared" si="3"/>
@@ -7103,19 +7103,19 @@
       </c>
       <c r="F33" s="22">
         <f t="shared" si="11"/>
-        <v>8301050.1955763269</v>
+        <v>4570640.5015814584</v>
       </c>
       <c r="G33" s="22">
         <f t="shared" si="12"/>
-        <v>11497.675604537701</v>
+        <v>6257.6749809778703</v>
       </c>
       <c r="H33" s="22">
         <f t="shared" si="13"/>
-        <v>574.50420002057899</v>
+        <v>312.67716037462702</v>
       </c>
       <c r="I33" s="22">
         <f t="shared" si="14"/>
-        <v>58064.948932737898</v>
+        <v>137019.15561186301</v>
       </c>
       <c r="J33" s="22">
         <f t="shared" si="15"/>
@@ -7123,7 +7123,7 @@
       </c>
       <c r="K33" s="4">
         <f t="shared" si="4"/>
-        <v>4857635.6200214876</v>
+        <v>2674662.3118393868</v>
       </c>
       <c r="L33" s="4">
         <f t="shared" si="5"/>
@@ -7131,43 +7131,43 @@
       </c>
       <c r="M33" s="4">
         <f t="shared" si="6"/>
-        <v>6519.9662474761199</v>
+        <v>3548.5285084534239</v>
       </c>
       <c r="N33" s="22">
         <f t="shared" si="7"/>
-        <v>325.78306450819838</v>
+        <v>177.30927555432766</v>
       </c>
       <c r="O33" s="4">
         <f t="shared" si="8"/>
-        <v>32926.786267431627</v>
+        <v>77699.206393894885</v>
       </c>
       <c r="P33" s="22">
         <f>+SUM(M33:$M$60)</f>
-        <v>371923.572130021</v>
+        <v>113136.0596742156</v>
       </c>
       <c r="Q33" s="22">
         <f>+SUM(N33:$N$60)</f>
-        <v>18542.630999355391</v>
+        <v>5645.0823501944251</v>
       </c>
       <c r="R33" s="22">
         <f>+SUM(O33:$O$60)</f>
-        <v>338944.32148405397</v>
+        <v>553004.35162043141</v>
       </c>
       <c r="S33" s="22">
         <f>+SUM(P33:$P$60)</f>
-        <v>5284080.3547593197</v>
+        <v>1207633.1233690821</v>
       </c>
       <c r="T33" s="22">
         <f>+SUM(Q33:$Q$60)</f>
-        <v>263309.38489967503</v>
+        <v>60233.602256251514</v>
       </c>
       <c r="U33" s="22">
         <f>+SUM(R33:$R$60)</f>
-        <v>2360213.4689847622</v>
+        <v>3113934.5269766669</v>
       </c>
       <c r="V33" s="23">
         <f t="shared" si="10"/>
-        <v>0.82126354741443308</v>
+        <v>0.71923574675310564</v>
       </c>
       <c r="W33" s="23"/>
       <c r="X33" s="14">
@@ -7263,8 +7263,8 @@
         <f t="shared" si="9"/>
         <v>7.75E-5</v>
       </c>
-      <c r="D34" s="26">
-        <v>7.0000000000000001E-3</v>
+      <c r="D34" s="30">
+        <v>0.03</v>
       </c>
       <c r="E34" s="20">
         <f t="shared" si="3"/>
@@ -7272,19 +7272,19 @@
       </c>
       <c r="F34" s="22">
         <f t="shared" si="11"/>
-        <v>8230913.06683903</v>
+        <v>4427050.9938282426</v>
       </c>
       <c r="G34" s="22">
         <f t="shared" si="12"/>
-        <v>12712.7699112891</v>
+        <v>6758.7381935732101</v>
       </c>
       <c r="H34" s="22">
         <f t="shared" si="13"/>
-        <v>635.17048858682404</v>
+        <v>337.68809398730099</v>
       </c>
       <c r="I34" s="22">
         <f t="shared" si="14"/>
-        <v>57569.5078596085</v>
+        <v>132703.458420957</v>
       </c>
       <c r="J34" s="22">
         <f t="shared" si="15"/>
@@ -7292,7 +7292,7 @@
       </c>
       <c r="K34" s="4">
         <f t="shared" si="4"/>
-        <v>4749151.3662208887</v>
+        <v>2554362.4510352416</v>
       </c>
       <c r="L34" s="4">
         <f t="shared" si="5"/>
@@ -7300,43 +7300,43 @@
       </c>
       <c r="M34" s="4">
         <f t="shared" si="6"/>
-        <v>7108.0681891690429</v>
+        <v>3779.0011372736371</v>
       </c>
       <c r="N34" s="22">
         <f t="shared" si="7"/>
-        <v>355.14173355829655</v>
+        <v>188.81093699342065</v>
       </c>
       <c r="O34" s="4">
         <f t="shared" si="8"/>
-        <v>32188.735447781411</v>
+        <v>74198.246171126695</v>
       </c>
       <c r="P34" s="22">
         <f>+SUM(M34:$M$60)</f>
-        <v>365403.60588254483</v>
+        <v>109587.53116576218</v>
       </c>
       <c r="Q34" s="22">
         <f>+SUM(N34:$N$60)</f>
-        <v>18216.847934847196</v>
+        <v>5467.7730746400975</v>
       </c>
       <c r="R34" s="22">
         <f>+SUM(O34:$O$60)</f>
-        <v>306017.53521662235</v>
+        <v>475305.14522653655</v>
       </c>
       <c r="S34" s="22">
         <f>+SUM(P34:$P$60)</f>
-        <v>4912156.782629298</v>
+        <v>1094497.0636948664</v>
       </c>
       <c r="T34" s="22">
         <f>+SUM(Q34:$Q$60)</f>
-        <v>244766.7539003196</v>
+        <v>54588.519906057089</v>
       </c>
       <c r="U34" s="22">
         <f>+SUM(R34:$R$60)</f>
-        <v>2021269.1475007078</v>
+        <v>2560930.1753562358</v>
       </c>
       <c r="V34" s="23">
         <f t="shared" si="10"/>
-        <v>0.82826168561423019</v>
+        <v>0.74256385094227584</v>
       </c>
       <c r="W34" s="23"/>
       <c r="X34" s="14">
@@ -7432,8 +7432,8 @@
         <f t="shared" si="9"/>
         <v>8.6500000000000002E-5</v>
       </c>
-      <c r="D35" s="26">
-        <v>7.0000000000000001E-3</v>
+      <c r="D35" s="30">
+        <v>0.03</v>
       </c>
       <c r="E35" s="20">
         <f t="shared" si="3"/>
@@ -7441,19 +7441,19 @@
       </c>
       <c r="F35" s="22">
         <f t="shared" si="11"/>
-        <v>8159995.618579546</v>
+        <v>4287251.1091197245</v>
       </c>
       <c r="G35" s="22">
         <f t="shared" si="12"/>
-        <v>14066.775232329401</v>
+        <v>7305.3742813920499</v>
       </c>
       <c r="H35" s="22">
         <f t="shared" si="13"/>
-        <v>702.76076799088696</v>
+        <v>364.96854152135302</v>
       </c>
       <c r="I35" s="22">
         <f t="shared" si="14"/>
-        <v>57068.092254842202</v>
+        <v>128500.72121073899</v>
       </c>
       <c r="J35" s="22">
         <f t="shared" si="15"/>
@@ -7461,7 +7461,7 @@
       </c>
       <c r="K35" s="4">
         <f t="shared" si="4"/>
-        <v>4642308.7921310291</v>
+        <v>2439063.0152574247</v>
       </c>
       <c r="L35" s="4">
         <f t="shared" si="5"/>
@@ -7469,43 +7469,43 @@
       </c>
       <c r="M35" s="4">
         <f t="shared" si="6"/>
-        <v>7755.0044123162106</v>
+        <v>4027.4482850633544</v>
       </c>
       <c r="N35" s="22">
         <f t="shared" si="7"/>
-        <v>387.43157309051378</v>
+        <v>201.20692931453155</v>
       </c>
       <c r="O35" s="4">
         <f t="shared" si="8"/>
-        <v>31461.603667458556</v>
+        <v>70842.367459231522</v>
       </c>
       <c r="P35" s="22">
         <f>+SUM(M35:$M$60)</f>
-        <v>358295.53769337578</v>
+        <v>105808.53002848855</v>
       </c>
       <c r="Q35" s="22">
         <f>+SUM(N35:$N$60)</f>
-        <v>17861.7062012889</v>
+        <v>5278.9621376466766</v>
       </c>
       <c r="R35" s="22">
         <f>+SUM(O35:$O$60)</f>
-        <v>273828.79976884089</v>
+        <v>401106.89905540989</v>
       </c>
       <c r="S35" s="22">
         <f>+SUM(P35:$P$60)</f>
-        <v>4546753.176746754</v>
+        <v>984909.53252910427</v>
       </c>
       <c r="T35" s="22">
         <f>+SUM(Q35:$Q$60)</f>
-        <v>226549.90596547243</v>
+        <v>49120.746831416996</v>
       </c>
       <c r="U35" s="22">
         <f>+SUM(R35:$R$60)</f>
-        <v>1715251.6122840857</v>
+        <v>2085625.0301296993</v>
       </c>
       <c r="V35" s="23">
         <f t="shared" si="10"/>
-        <v>0.8354599989443402</v>
+        <v>0.76677758093108406</v>
       </c>
       <c r="W35" s="23"/>
       <c r="X35" s="14">
@@ -7601,8 +7601,8 @@
         <f t="shared" si="9"/>
         <v>9.6500000000000015E-5</v>
       </c>
-      <c r="D36" s="26">
-        <v>6.0000000000000001E-3</v>
+      <c r="D36" s="30">
+        <v>0.02</v>
       </c>
       <c r="E36" s="20">
         <f t="shared" si="3"/>
@@ -7610,19 +7610,19 @@
       </c>
       <c r="F36" s="22">
         <f t="shared" si="11"/>
-        <v>8088157.9903243836</v>
+        <v>4151080.0450860714</v>
       </c>
       <c r="G36" s="22">
         <f t="shared" si="12"/>
-        <v>15562.563556638101</v>
+        <v>7931.0859487839698</v>
       </c>
       <c r="H36" s="22">
         <f t="shared" si="13"/>
-        <v>777.41479440412797</v>
+        <v>396.19073874531398</v>
       </c>
       <c r="I36" s="22">
         <f t="shared" si="14"/>
-        <v>48479.778245012603</v>
+        <v>82937.483130197303</v>
       </c>
       <c r="J36" s="22">
         <f t="shared" si="15"/>
@@ -7630,7 +7630,7 @@
       </c>
       <c r="K36" s="4">
         <f t="shared" si="4"/>
-        <v>4537010.9550303435</v>
+        <v>2328527.1704995497</v>
       </c>
       <c r="L36" s="4">
         <f t="shared" si="5"/>
@@ -7638,43 +7638,43 @@
       </c>
       <c r="M36" s="4">
         <f t="shared" si="6"/>
-        <v>8459.5009148502395</v>
+        <v>4311.1810335949322</v>
       </c>
       <c r="N36" s="22">
         <f t="shared" si="7"/>
-        <v>422.5872646588906</v>
+        <v>215.3614283837951</v>
       </c>
       <c r="O36" s="4">
         <f t="shared" si="8"/>
-        <v>26352.646009949261</v>
+        <v>45083.171025252697</v>
       </c>
       <c r="P36" s="22">
         <f>+SUM(M36:$M$60)</f>
-        <v>350540.53328105964</v>
+        <v>101781.08174342519</v>
       </c>
       <c r="Q36" s="22">
         <f>+SUM(N36:$N$60)</f>
-        <v>17474.274628198385</v>
+        <v>5077.7552083321452</v>
       </c>
       <c r="R36" s="22">
         <f>+SUM(O36:$O$60)</f>
-        <v>242367.19610138235</v>
+        <v>330264.53159617836</v>
       </c>
       <c r="S36" s="22">
         <f>+SUM(P36:$P$60)</f>
-        <v>4188457.6390533783</v>
+        <v>879101.00250061578</v>
       </c>
       <c r="T36" s="22">
         <f>+SUM(Q36:$Q$60)</f>
-        <v>208688.19976418352</v>
+        <v>43841.784693770314</v>
       </c>
       <c r="U36" s="22">
         <f>+SUM(R36:$R$60)</f>
-        <v>1441422.8125152448</v>
+        <v>1684518.1310742896</v>
       </c>
       <c r="V36" s="23">
         <f t="shared" si="10"/>
-        <v>0.84288041097115995</v>
+        <v>0.79193077430208092</v>
       </c>
       <c r="W36" s="23"/>
       <c r="X36" s="14">
@@ -7770,8 +7770,8 @@
         <f t="shared" si="9"/>
         <v>1.0800000000000001E-4</v>
       </c>
-      <c r="D37" s="26">
-        <v>6.0000000000000001E-3</v>
+      <c r="D37" s="30">
+        <v>0.02</v>
       </c>
       <c r="E37" s="20">
         <f t="shared" si="3"/>
@@ -7779,19 +7779,19 @@
       </c>
       <c r="F37" s="22">
         <f t="shared" si="11"/>
-        <v>8023338.2337283287</v>
+        <v>4059815.2852683445</v>
       </c>
       <c r="G37" s="22">
         <f t="shared" si="12"/>
-        <v>17277.486318453601</v>
+        <v>8681.0402045315004</v>
       </c>
       <c r="H37" s="22">
         <f t="shared" si="13"/>
-        <v>862.98793300986404</v>
+        <v>433.60664881456597</v>
       </c>
       <c r="I37" s="22">
         <f t="shared" si="14"/>
-        <v>48085.441416554197</v>
+        <v>81104.233830065597</v>
       </c>
       <c r="J37" s="22">
         <f t="shared" si="15"/>
@@ -7799,7 +7799,7 @@
       </c>
       <c r="K37" s="4">
         <f t="shared" si="4"/>
-        <v>4437633.2326079691</v>
+        <v>2245445.8111240375</v>
       </c>
       <c r="L37" s="4">
         <f t="shared" si="5"/>
@@ -7807,43 +7807,43 @@
       </c>
       <c r="M37" s="4">
         <f t="shared" si="6"/>
-        <v>9260.197809717527</v>
+        <v>4652.7688117577636</v>
       </c>
       <c r="N37" s="22">
         <f t="shared" si="7"/>
-        <v>462.53481668425144</v>
+        <v>232.39974065804864</v>
       </c>
       <c r="O37" s="4">
         <f t="shared" si="8"/>
-        <v>25772.308024303493</v>
+        <v>43469.3585993366</v>
       </c>
       <c r="P37" s="22">
         <f>+SUM(M37:$M$60)</f>
-        <v>342081.03236620937</v>
+        <v>97469.900709830254</v>
       </c>
       <c r="Q37" s="22">
         <f>+SUM(N37:$N$60)</f>
-        <v>17051.687363539495</v>
+        <v>4862.3937799483492</v>
       </c>
       <c r="R37" s="22">
         <f>+SUM(O37:$O$60)</f>
-        <v>216014.55009143314</v>
+        <v>285181.3605709257</v>
       </c>
       <c r="S37" s="22">
         <f>+SUM(P37:$P$60)</f>
-        <v>3837917.1057723179</v>
+        <v>777319.92075719056</v>
       </c>
       <c r="T37" s="22">
         <f>+SUM(Q37:$Q$60)</f>
-        <v>191213.9251359851</v>
+        <v>38764.029485438172</v>
       </c>
       <c r="U37" s="22">
         <f>+SUM(R37:$R$60)</f>
-        <v>1199055.6164138624</v>
+        <v>1354253.5994781109</v>
       </c>
       <c r="V37" s="23">
         <f t="shared" si="10"/>
-        <v>0.8496899585045119</v>
+        <v>0.80973339999571969</v>
       </c>
       <c r="W37" s="23"/>
       <c r="X37" s="14">
@@ -7939,8 +7939,8 @@
         <f t="shared" si="9"/>
         <v>1.205E-4</v>
       </c>
-      <c r="D38" s="26">
-        <v>6.0000000000000001E-3</v>
+      <c r="D38" s="30">
+        <v>0.02</v>
       </c>
       <c r="E38" s="20">
         <f t="shared" si="3"/>
@@ -7948,19 +7948,19 @@
       </c>
       <c r="F38" s="22">
         <f t="shared" si="11"/>
-        <v>7957112.3180603115</v>
+        <v>3969596.4045849331</v>
       </c>
       <c r="G38" s="22">
         <f t="shared" si="12"/>
-        <v>19117.958838042199</v>
+        <v>9470.48943033047</v>
       </c>
       <c r="H38" s="22">
         <f t="shared" si="13"/>
-        <v>954.80361179972999</v>
+        <v>472.98237171624203</v>
       </c>
       <c r="I38" s="22">
         <f t="shared" si="14"/>
-        <v>47682.270956377099</v>
+        <v>79291.483218633904</v>
       </c>
       <c r="J38" s="22">
         <f t="shared" si="15"/>
@@ -7968,7 +7968,7 @@
       </c>
       <c r="K38" s="4">
         <f t="shared" si="4"/>
-        <v>4339382.1208300134</v>
+        <v>2164804.8910746067</v>
       </c>
       <c r="L38" s="4">
         <f t="shared" si="5"/>
@@ -7976,43 +7976,43 @@
       </c>
       <c r="M38" s="4">
         <f t="shared" si="6"/>
-        <v>10103.162326997513</v>
+        <v>5004.8173469412804</v>
       </c>
       <c r="N38" s="22">
         <f t="shared" si="7"/>
-        <v>504.57980175273036</v>
+        <v>249.95438685371877</v>
       </c>
       <c r="O38" s="4">
         <f t="shared" si="8"/>
-        <v>25198.386902766775</v>
+        <v>41902.733073793715</v>
       </c>
       <c r="P38" s="22">
         <f>+SUM(M38:$M$60)</f>
-        <v>332820.83455649187</v>
+        <v>92817.13189807249</v>
       </c>
       <c r="Q38" s="22">
         <f>+SUM(N38:$N$60)</f>
-        <v>16589.152546855243</v>
+        <v>4629.9940392903009</v>
       </c>
       <c r="R38" s="22">
         <f>+SUM(O38:$O$60)</f>
-        <v>190242.24206712961</v>
+        <v>241712.00197158905</v>
       </c>
       <c r="S38" s="22">
         <f>+SUM(P38:$P$60)</f>
-        <v>3495836.0734061087</v>
+        <v>679850.02004736033</v>
       </c>
       <c r="T38" s="22">
         <f>+SUM(Q38:$Q$60)</f>
-        <v>174162.2377724456</v>
+        <v>33901.635705489811</v>
       </c>
       <c r="U38" s="22">
         <f>+SUM(R38:$R$60)</f>
-        <v>983041.06632242934</v>
+        <v>1069072.2389071849</v>
       </c>
       <c r="V38" s="23">
         <f t="shared" si="10"/>
-        <v>0.85676180734698226</v>
+        <v>0.82813659103932546</v>
       </c>
       <c r="W38" s="23"/>
       <c r="X38" s="14">
@@ -8108,8 +8108,8 @@
         <f t="shared" si="9"/>
         <v>1.35E-4</v>
       </c>
-      <c r="D39" s="26">
-        <v>6.0000000000000001E-3</v>
+      <c r="D39" s="30">
+        <v>0.02</v>
       </c>
       <c r="E39" s="20">
         <f t="shared" si="3"/>
@@ -8117,19 +8117,19 @@
       </c>
       <c r="F39" s="22">
         <f t="shared" si="11"/>
-        <v>7889357.284654092</v>
+        <v>3880361.449564252</v>
       </c>
       <c r="G39" s="22">
         <f t="shared" si="12"/>
-        <v>21235.927352701299</v>
+        <v>10371.5060307698</v>
       </c>
       <c r="H39" s="22">
         <f t="shared" si="13"/>
-        <v>1060.43452186898</v>
+        <v>517.910183818821</v>
       </c>
       <c r="I39" s="22">
         <f t="shared" si="14"/>
-        <v>47269.049037724697</v>
+        <v>77497.227816148603</v>
       </c>
       <c r="J39" s="22">
         <f t="shared" si="15"/>
@@ -8137,7 +8137,7 @@
       </c>
       <c r="K39" s="4">
         <f t="shared" si="4"/>
-        <v>4242190.1746704979</v>
+        <v>2086511.0580719989</v>
       </c>
       <c r="L39" s="4">
         <f t="shared" si="5"/>
@@ -8145,43 +8145,43 @@
       </c>
       <c r="M39" s="4">
         <f t="shared" si="6"/>
-        <v>11065.298704463075</v>
+        <v>5404.2288966019469</v>
       </c>
       <c r="N39" s="22">
         <f t="shared" si="7"/>
-        <v>552.55532504504106</v>
+        <v>269.86487525865675</v>
       </c>
       <c r="O39" s="4">
         <f t="shared" si="8"/>
-        <v>24630.24752304038</v>
+        <v>40381.093809139791</v>
       </c>
       <c r="P39" s="22">
         <f>+SUM(M39:$M$60)</f>
-        <v>322717.67222949426</v>
+        <v>87812.314551131203</v>
       </c>
       <c r="Q39" s="22">
         <f>+SUM(N39:$N$60)</f>
-        <v>16084.57274510251</v>
+        <v>4380.0396524365824</v>
       </c>
       <c r="R39" s="22">
         <f>+SUM(O39:$O$60)</f>
-        <v>165043.85516436285</v>
+        <v>199809.26889779535</v>
       </c>
       <c r="S39" s="22">
         <f>+SUM(P39:$P$60)</f>
-        <v>3163015.2388496171</v>
+        <v>587032.8881492879</v>
       </c>
       <c r="T39" s="22">
         <f>+SUM(Q39:$Q$60)</f>
-        <v>157573.08522559036</v>
+        <v>29271.641666199517</v>
       </c>
       <c r="U39" s="22">
         <f>+SUM(R39:$R$60)</f>
-        <v>792798.82425529975</v>
+        <v>827360.23693559598</v>
       </c>
       <c r="V39" s="23">
         <f t="shared" si="10"/>
-        <v>0.86411981165373142</v>
+        <v>0.84718088173566586</v>
       </c>
       <c r="W39" s="23"/>
       <c r="X39" s="14">
@@ -8277,8 +8277,8 @@
         <f t="shared" si="9"/>
         <v>1.5100000000000001E-4</v>
       </c>
-      <c r="D40" s="26">
-        <v>5.0000000000000001E-3</v>
+      <c r="D40" s="30">
+        <v>0.02</v>
       </c>
       <c r="E40" s="20">
         <f t="shared" si="3"/>
@@ -8286,19 +8286,19 @@
       </c>
       <c r="F40" s="22">
         <f t="shared" si="11"/>
-        <v>7819791.8737417972</v>
+        <v>3791974.8055335144</v>
       </c>
       <c r="G40" s="22">
         <f t="shared" si="12"/>
-        <v>23554.953496785201</v>
+        <v>11336.390311490401</v>
       </c>
       <c r="H40" s="22">
         <f t="shared" si="13"/>
-        <v>1176.05806823441</v>
+        <v>566.00635158554996</v>
       </c>
       <c r="I40" s="22">
         <f t="shared" si="14"/>
-        <v>39036.972426106797</v>
+        <v>75719.2612356686</v>
       </c>
       <c r="J40" s="22">
         <f t="shared" si="15"/>
@@ -8306,7 +8306,7 @@
       </c>
       <c r="K40" s="4">
         <f t="shared" si="4"/>
-        <v>4145909.3897709502</v>
+        <v>2010435.0864920947</v>
       </c>
       <c r="L40" s="4">
         <f t="shared" si="5"/>
@@ -8314,43 +8314,43 @@
       </c>
       <c r="M40" s="4">
         <f t="shared" si="6"/>
-        <v>12101.808177440884</v>
+        <v>5824.2874898046412</v>
       </c>
       <c r="N40" s="22">
         <f t="shared" si="7"/>
-        <v>604.22234114140645</v>
+        <v>290.79659592774573</v>
       </c>
       <c r="O40" s="4">
         <f t="shared" si="8"/>
-        <v>20055.991712879819</v>
+        <v>38902.219651448671</v>
       </c>
       <c r="P40" s="22">
         <f>+SUM(M40:$M$60)</f>
-        <v>311652.37352503126</v>
+        <v>82408.085654529263</v>
       </c>
       <c r="Q40" s="22">
         <f>+SUM(N40:$N$60)</f>
-        <v>15532.017420057471</v>
+        <v>4110.1747771779255</v>
       </c>
       <c r="R40" s="22">
         <f>+SUM(O40:$O$60)</f>
-        <v>140413.60764132248</v>
+        <v>159428.17508865558</v>
       </c>
       <c r="S40" s="22">
         <f>+SUM(P40:$P$60)</f>
-        <v>2840297.5666201222</v>
+        <v>499220.57359815651</v>
       </c>
       <c r="T40" s="22">
         <f>+SUM(Q40:$Q$60)</f>
-        <v>141488.5124804879</v>
+        <v>24891.602013762935</v>
       </c>
       <c r="U40" s="22">
         <f>+SUM(R40:$R$60)</f>
-        <v>627754.96909093671</v>
+        <v>627550.96803780063</v>
       </c>
       <c r="V40" s="23">
         <f t="shared" si="10"/>
-        <v>0.87180708143606411</v>
+        <v>0.86692770993567059</v>
       </c>
       <c r="W40" s="23"/>
       <c r="X40" s="14">
@@ -8446,8 +8446,8 @@
         <f>$E$3*B41</f>
         <v>1.6900000000000002E-4</v>
       </c>
-      <c r="D41" s="26">
-        <v>5.0000000000000001E-3</v>
+      <c r="D41" s="30">
+        <v>0.01</v>
       </c>
       <c r="E41" s="20">
         <f t="shared" si="3"/>
@@ -8455,19 +8455,19 @@
       </c>
       <c r="F41" s="22">
         <f t="shared" si="11"/>
-        <v>7756023.8897506706</v>
+        <v>3704353.1476347698</v>
       </c>
       <c r="G41" s="22">
         <f t="shared" si="12"/>
-        <v>26147.612685500699</v>
+        <v>12457.0573605095</v>
       </c>
       <c r="H41" s="22">
         <f t="shared" si="13"/>
-        <v>1305.2814572862501</v>
+        <v>621.85279323954103</v>
       </c>
       <c r="I41" s="22">
         <f t="shared" si="14"/>
-        <v>38711.309664786502</v>
+        <v>36977.803019744402</v>
       </c>
       <c r="J41" s="22">
         <f t="shared" si="15"/>
@@ -8475,7 +8475,7 @@
       </c>
       <c r="K41" s="4">
         <f t="shared" si="4"/>
-        <v>4054523.7851398569</v>
+        <v>1936480.3614762577</v>
       </c>
       <c r="L41" s="4">
         <f t="shared" si="5"/>
@@ -8483,43 +8483,43 @@
       </c>
       <c r="M41" s="4">
         <f t="shared" si="6"/>
-        <v>13245.737966737297</v>
+        <v>6310.4391065660056</v>
       </c>
       <c r="N41" s="22">
         <f t="shared" si="7"/>
-        <v>661.22350686500522</v>
+        <v>315.01534202019627</v>
       </c>
       <c r="O41" s="4">
         <f t="shared" si="8"/>
-        <v>19610.198083334821</v>
+        <v>18732.046220677083</v>
       </c>
       <c r="P41" s="22">
         <f>+SUM(M41:$M$60)</f>
-        <v>299550.56534759037</v>
+        <v>76583.79816472462</v>
       </c>
       <c r="Q41" s="22">
         <f>+SUM(N41:$N$60)</f>
-        <v>14927.795078916064</v>
+        <v>3819.3781812501798</v>
       </c>
       <c r="R41" s="22">
         <f>+SUM(O41:$O$60)</f>
-        <v>120357.61592844265</v>
+        <v>120525.95543720687</v>
       </c>
       <c r="S41" s="22">
         <f>+SUM(P41:$P$60)</f>
-        <v>2528645.1930950913</v>
+        <v>416812.48794362723</v>
       </c>
       <c r="T41" s="22">
         <f>+SUM(Q41:$Q$60)</f>
-        <v>125956.4950604304</v>
+        <v>20781.427236585012</v>
       </c>
       <c r="U41" s="22">
         <f>+SUM(R41:$R$60)</f>
-        <v>487341.36144961434</v>
+        <v>468122.79294914514</v>
       </c>
       <c r="V41" s="23">
         <f t="shared" si="10"/>
-        <v>0.87897484945774729</v>
+        <v>0.887433757873197</v>
       </c>
       <c r="W41" s="23"/>
       <c r="X41" s="14">
@@ -8615,8 +8615,8 @@
         <f t="shared" si="9"/>
         <v>1.885E-4</v>
       </c>
-      <c r="D42" s="26">
-        <v>5.0000000000000001E-3</v>
+      <c r="D42" s="30">
+        <v>0.01</v>
       </c>
       <c r="E42" s="20">
         <f t="shared" si="3"/>
@@ -8624,19 +8624,19 @@
       </c>
       <c r="F42" s="22">
         <f t="shared" si="11"/>
-        <v>7689859.6859430969</v>
+        <v>3654296.4344612765</v>
       </c>
       <c r="G42" s="22">
         <f t="shared" si="12"/>
-        <v>28915.568539247601</v>
+        <v>13706.5221086533</v>
       </c>
       <c r="H42" s="22">
         <f t="shared" si="13"/>
-        <v>1443.1891552054401</v>
+        <v>684.098742030361</v>
       </c>
       <c r="I42" s="22">
         <f t="shared" si="14"/>
-        <v>38373.204486748902</v>
+        <v>36470.643174702403</v>
       </c>
       <c r="J42" s="22">
         <f t="shared" si="15"/>
@@ -8644,7 +8644,7 @@
       </c>
       <c r="K42" s="4">
         <f t="shared" si="4"/>
-        <v>3963649.398348562</v>
+        <v>1883564.9095544387</v>
       </c>
       <c r="L42" s="4">
         <f t="shared" si="5"/>
@@ -8652,43 +8652,43 @@
       </c>
       <c r="M42" s="4">
         <f t="shared" si="6"/>
-        <v>14442.81852713588</v>
+        <v>6846.1670115446559</v>
       </c>
       <c r="N42" s="22">
         <f t="shared" si="7"/>
-        <v>720.84763059979855</v>
+        <v>341.695304118808</v>
       </c>
       <c r="O42" s="4">
         <f t="shared" si="8"/>
-        <v>19166.741541136988</v>
+        <v>18216.445587960749</v>
       </c>
       <c r="P42" s="22">
         <f>+SUM(M42:$M$60)</f>
-        <v>286304.82738085306</v>
+        <v>70273.359058158632</v>
       </c>
       <c r="Q42" s="22">
         <f>+SUM(N42:$N$60)</f>
-        <v>14266.571572051058</v>
+        <v>3504.3628392299834</v>
       </c>
       <c r="R42" s="22">
         <f>+SUM(O42:$O$60)</f>
-        <v>100747.41784510783</v>
+        <v>101793.90921652981</v>
       </c>
       <c r="S42" s="22">
         <f>+SUM(P42:$P$60)</f>
-        <v>2229094.6277474998</v>
+        <v>340228.68977890263</v>
       </c>
       <c r="T42" s="22">
         <f>+SUM(Q42:$Q$60)</f>
-        <v>111028.69998151435</v>
+        <v>16962.049055334832</v>
       </c>
       <c r="U42" s="22">
         <f>+SUM(R42:$R$60)</f>
-        <v>366983.74552117166</v>
+        <v>347596.8375119383</v>
       </c>
       <c r="V42" s="23">
         <f t="shared" si="10"/>
-        <v>0.88653762348177312</v>
+        <v>0.89958986449317968</v>
       </c>
       <c r="W42" s="23"/>
       <c r="X42" s="14">
@@ -8784,8 +8784,8 @@
         <f t="shared" si="9"/>
         <v>2.0899999999999998E-4</v>
       </c>
-      <c r="D43" s="26">
-        <v>5.0000000000000001E-3</v>
+      <c r="D43" s="30">
+        <v>0.01</v>
       </c>
       <c r="E43" s="20">
         <f t="shared" si="3"/>
@@ -8793,19 +8793,19 @@
       </c>
       <c r="F43" s="22">
         <f t="shared" si="11"/>
-        <v>7621127.7237618947</v>
+        <v>3603435.1704358906</v>
       </c>
       <c r="G43" s="22">
         <f t="shared" si="12"/>
-        <v>31773.352438272399</v>
+        <v>14985.4810709257</v>
       </c>
       <c r="H43" s="22">
         <f t="shared" si="13"/>
-        <v>1585.5129926915599</v>
+        <v>747.78621443378097</v>
       </c>
       <c r="I43" s="22">
         <f t="shared" si="14"/>
-        <v>38022.0241173225</v>
+        <v>35955.282189626298</v>
       </c>
       <c r="J43" s="22">
         <f t="shared" si="15"/>
@@ -8813,7 +8813,7 @@
       </c>
       <c r="K43" s="4">
         <f t="shared" si="4"/>
-        <v>3873219.9438823657</v>
+        <v>1831342.7453922953</v>
       </c>
       <c r="L43" s="4">
         <f t="shared" si="5"/>
@@ -8821,43 +8821,43 @@
       </c>
       <c r="M43" s="4">
         <f t="shared" si="6"/>
-        <v>15648.01886930961</v>
+        <v>7380.1809556951284</v>
       </c>
       <c r="N43" s="22">
         <f t="shared" si="7"/>
-        <v>780.84732403900125</v>
+        <v>368.27630374862764</v>
       </c>
       <c r="O43" s="4">
         <f t="shared" si="8"/>
-        <v>18725.419421607548</v>
+        <v>17707.572257213651</v>
       </c>
       <c r="P43" s="22">
         <f>+SUM(M43:$M$60)</f>
-        <v>271862.00885371718</v>
+        <v>63427.192046613971</v>
       </c>
       <c r="Q43" s="22">
         <f>+SUM(N43:$N$60)</f>
-        <v>13545.723941451261</v>
+        <v>3162.6675351111753</v>
       </c>
       <c r="R43" s="22">
         <f>+SUM(O43:$O$60)</f>
-        <v>81580.676303970846</v>
+        <v>83577.463628569065</v>
       </c>
       <c r="S43" s="22">
         <f>+SUM(P43:$P$60)</f>
-        <v>1942789.8003666468</v>
+        <v>269955.33072074404</v>
       </c>
       <c r="T43" s="22">
         <f>+SUM(Q43:$Q$60)</f>
-        <v>96762.128409463287</v>
+        <v>13457.686216104848</v>
       </c>
       <c r="U43" s="22">
         <f>+SUM(R43:$R$60)</f>
-        <v>266236.32767606381</v>
+        <v>245802.92829540846</v>
       </c>
       <c r="V43" s="23">
         <f t="shared" si="10"/>
-        <v>0.89453295863661875</v>
+        <v>0.91228727000998655</v>
       </c>
       <c r="W43" s="23"/>
       <c r="X43" s="14">
@@ -8953,8 +8953,8 @@
         <f t="shared" si="9"/>
         <v>2.3050000000000002E-4</v>
       </c>
-      <c r="D44" s="26">
-        <v>4.0000000000000001E-3</v>
+      <c r="D44" s="30">
+        <v>0.01</v>
       </c>
       <c r="E44" s="20">
         <f t="shared" si="3"/>
@@ -8962,19 +8962,19 @@
       </c>
       <c r="F44" s="22">
         <f t="shared" si="11"/>
-        <v>7549746.8342136089</v>
+        <v>3551746.6209609052</v>
       </c>
       <c r="G44" s="22">
         <f t="shared" si="12"/>
-        <v>34730.721062944598</v>
+        <v>16289.806546416799</v>
       </c>
       <c r="H44" s="22">
         <f t="shared" si="13"/>
-        <v>1732.7330350270099</v>
+        <v>812.70659155104397</v>
       </c>
       <c r="I44" s="22">
         <f t="shared" si="14"/>
-        <v>30125.9062601511</v>
+        <v>35431.514497274497</v>
       </c>
       <c r="J44" s="22">
         <f t="shared" si="15"/>
@@ -8982,7 +8982,7 @@
       </c>
       <c r="K44" s="4">
         <f t="shared" si="4"/>
-        <v>3783218.3761155871</v>
+        <v>1779799.1613218591</v>
       </c>
       <c r="L44" s="4">
         <f t="shared" si="5"/>
@@ -8990,43 +8990,43 @@
       </c>
       <c r="M44" s="4">
         <f t="shared" si="6"/>
-        <v>16864.995263713583</v>
+        <v>7910.2161384505807</v>
       </c>
       <c r="N44" s="22">
         <f t="shared" si="7"/>
-        <v>841.40304418237702</v>
+        <v>394.64463730702334</v>
       </c>
       <c r="O44" s="4">
         <f t="shared" si="8"/>
-        <v>14628.929398606946</v>
+        <v>17205.29565452307</v>
       </c>
       <c r="P44" s="22">
         <f>+SUM(M44:$M$60)</f>
-        <v>256213.98998440756</v>
+        <v>56047.011090918837</v>
       </c>
       <c r="Q44" s="22">
         <f>+SUM(N44:$N$60)</f>
-        <v>12764.876617412259</v>
+        <v>2794.3912313625478</v>
       </c>
       <c r="R44" s="22">
         <f>+SUM(O44:$O$60)</f>
-        <v>62855.256882363297</v>
+        <v>65869.891371355392</v>
       </c>
       <c r="S44" s="22">
         <f>+SUM(P44:$P$60)</f>
-        <v>1670927.7915129298</v>
+        <v>206528.13867413008</v>
       </c>
       <c r="T44" s="22">
         <f>+SUM(Q44:$Q$60)</f>
-        <v>83216.404468012013</v>
+        <v>10295.018680993675</v>
       </c>
       <c r="U44" s="22">
         <f>+SUM(R44:$R$60)</f>
-        <v>184655.65137209295</v>
+        <v>162225.4646668394</v>
       </c>
       <c r="V44" s="23">
         <f t="shared" si="10"/>
-        <v>0.90299053472756496</v>
+        <v>0.92556378174452947</v>
       </c>
       <c r="W44" s="23"/>
       <c r="X44" s="14">
@@ -9122,8 +9122,8 @@
         <f t="shared" si="9"/>
         <v>2.5400000000000005E-4</v>
       </c>
-      <c r="D45" s="26">
-        <v>4.0000000000000001E-3</v>
+      <c r="D45" s="30">
+        <v>0.01</v>
       </c>
       <c r="E45" s="20">
         <f t="shared" si="3"/>
@@ -9131,19 +9131,19 @@
       </c>
       <c r="F45" s="22">
         <f t="shared" si="11"/>
-        <v>7483157.4738554861</v>
+        <v>3499212.5933256629</v>
       </c>
       <c r="G45" s="22">
         <f t="shared" si="12"/>
-        <v>37933.5929090434</v>
+        <v>17684.873709987201</v>
       </c>
       <c r="H45" s="22">
         <f t="shared" si="13"/>
-        <v>1892.10237615449</v>
+        <v>882.10973447446804</v>
       </c>
       <c r="I45" s="22">
         <f t="shared" si="14"/>
-        <v>29852.809227158599</v>
+        <v>34898.813221152603</v>
       </c>
       <c r="J45" s="22">
         <f t="shared" si="15"/>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="K45" s="4">
         <f t="shared" si="4"/>
-        <v>3697345.2746415199</v>
+        <v>1728922.2085864916</v>
       </c>
       <c r="L45" s="4">
         <f t="shared" si="5"/>
@@ -9159,43 +9159,43 @@
       </c>
       <c r="M45" s="4">
         <f t="shared" si="6"/>
-        <v>18162.369432053238</v>
+        <v>8467.4080425273751</v>
       </c>
       <c r="N45" s="22">
         <f t="shared" si="7"/>
-        <v>905.92690340152171</v>
+        <v>422.34867958727443</v>
       </c>
       <c r="O45" s="4">
         <f t="shared" si="8"/>
-        <v>14293.340234560321</v>
+        <v>16709.33570628603</v>
       </c>
       <c r="P45" s="22">
         <f>+SUM(M45:$M$60)</f>
-        <v>239348.994720694</v>
+        <v>48136.794952468263</v>
       </c>
       <c r="Q45" s="22">
         <f>+SUM(N45:$N$60)</f>
-        <v>11923.47357322988</v>
+        <v>2399.7465940555244</v>
       </c>
       <c r="R45" s="22">
         <f>+SUM(O45:$O$60)</f>
-        <v>48226.327483756351</v>
+        <v>48664.595716832329</v>
       </c>
       <c r="S45" s="22">
         <f>+SUM(P45:$P$60)</f>
-        <v>1414713.8015285223</v>
+        <v>150481.12758321126</v>
       </c>
       <c r="T45" s="22">
         <f>+SUM(Q45:$Q$60)</f>
-        <v>70451.52785059977</v>
+        <v>7500.6274496311253</v>
       </c>
       <c r="U45" s="22">
         <f>+SUM(R45:$R$60)</f>
-        <v>121800.39448972965</v>
+        <v>96355.573295484006</v>
       </c>
       <c r="V45" s="23">
         <f t="shared" si="10"/>
-        <v>0.9110258543539429</v>
+        <v>0.93945936310505906</v>
       </c>
       <c r="W45" s="23"/>
       <c r="X45" s="14">
@@ -9291,8 +9291,8 @@
         <f t="shared" si="9"/>
         <v>2.7799999999999998E-4</v>
       </c>
-      <c r="D46" s="26">
-        <v>4.0000000000000001E-3</v>
+      <c r="D46" s="30">
+        <v>0.01</v>
       </c>
       <c r="E46" s="20">
         <f t="shared" si="3"/>
@@ -9300,19 +9300,19 @@
       </c>
       <c r="F46" s="22">
         <f t="shared" si="11"/>
-        <v>7413478.9693431295</v>
+        <v>3445746.7966600484</v>
       </c>
       <c r="G46" s="22">
         <f t="shared" si="12"/>
-        <v>41130.787209188202</v>
+        <v>19059.910732583201</v>
       </c>
       <c r="H46" s="22">
         <f t="shared" si="13"/>
-        <v>2051.1072849499401</v>
+        <v>950.47832552457703</v>
       </c>
       <c r="I46" s="22">
         <f t="shared" si="14"/>
-        <v>29567.3675557926</v>
+        <v>34356.899932660803</v>
       </c>
       <c r="J46" s="22">
         <f t="shared" si="15"/>
@@ -9320,7 +9320,7 @@
       </c>
       <c r="K46" s="4">
         <f t="shared" si="4"/>
-        <v>3611630.2898459095</v>
+        <v>1678667.1350144278</v>
       </c>
       <c r="L46" s="4">
         <f t="shared" si="5"/>
@@ -9328,43 +9328,43 @@
       </c>
       <c r="M46" s="4">
         <f t="shared" si="6"/>
-        <v>19417.425615756616</v>
+        <v>8997.9896813212508</v>
       </c>
       <c r="N46" s="22">
         <f t="shared" si="7"/>
-        <v>968.30685327984622</v>
+        <v>448.71113434803237</v>
       </c>
       <c r="O46" s="4">
         <f t="shared" si="8"/>
-        <v>13958.453001358681</v>
+        <v>16219.542442440932</v>
       </c>
       <c r="P46" s="22">
         <f>+SUM(M46:$M$60)</f>
-        <v>221186.62528864076</v>
+        <v>39669.386909940877</v>
       </c>
       <c r="Q46" s="22">
         <f>+SUM(N46:$N$60)</f>
-        <v>11017.54666982836</v>
+        <v>1977.3979144682501</v>
       </c>
       <c r="R46" s="22">
         <f>+SUM(O46:$O$60)</f>
-        <v>33932.987249196027</v>
+        <v>31955.260010546303</v>
       </c>
       <c r="S46" s="22">
         <f>+SUM(P46:$P$60)</f>
-        <v>1175364.8068078284</v>
+        <v>102344.33263074297</v>
       </c>
       <c r="T46" s="22">
         <f>+SUM(Q46:$Q$60)</f>
-        <v>58528.054277369898</v>
+        <v>5100.8808555756004</v>
       </c>
       <c r="U46" s="22">
         <f>+SUM(R46:$R$60)</f>
-        <v>73574.067005973295</v>
+        <v>47690.977578651669</v>
       </c>
       <c r="V46" s="23">
         <f t="shared" si="10"/>
-        <v>0.91958848997562315</v>
+        <v>0.95403644791351616</v>
       </c>
       <c r="W46" s="23"/>
       <c r="X46" s="14">
@@ -9460,8 +9460,8 @@
         <f t="shared" si="9"/>
         <v>3.0450000000000003E-4</v>
       </c>
-      <c r="D47" s="26">
-        <v>2E-3</v>
+      <c r="D47" s="30">
+        <v>0.01</v>
       </c>
       <c r="E47" s="20">
         <f t="shared" si="3"/>
@@ -9469,19 +9469,19 @@
       </c>
       <c r="F47" s="22">
         <f t="shared" si="11"/>
-        <v>7340729.7072931984</v>
+        <v>3391379.5076692803</v>
       </c>
       <c r="G47" s="22">
         <f t="shared" si="12"/>
-        <v>44653.539336904701</v>
+        <v>20547.1049226172</v>
       </c>
       <c r="H47" s="22">
         <f t="shared" si="13"/>
-        <v>2226.2174070814199</v>
+        <v>1024.3829117047001</v>
       </c>
       <c r="I47" s="22">
         <f t="shared" si="14"/>
-        <v>14634.525924816</v>
+        <v>33805.379917861603</v>
       </c>
       <c r="J47" s="22">
         <f t="shared" si="15"/>
@@ -9489,7 +9489,7 @@
       </c>
       <c r="K47" s="4">
         <f t="shared" si="4"/>
-        <v>3526115.7333900407</v>
+        <v>1629047.3994715065</v>
       </c>
       <c r="L47" s="4">
         <f t="shared" si="5"/>
@@ -9497,43 +9497,43 @@
       </c>
       <c r="M47" s="4">
         <f t="shared" si="6"/>
-        <v>20785.315388529518</v>
+        <v>9564.2599104084857</v>
       </c>
       <c r="N47" s="22">
         <f t="shared" si="7"/>
-        <v>1036.2589755876058</v>
+        <v>476.82943423042678</v>
       </c>
       <c r="O47" s="4">
         <f t="shared" si="8"/>
-        <v>6812.0745057607246</v>
+        <v>15735.71756810537</v>
       </c>
       <c r="P47" s="22">
         <f>+SUM(M47:$M$60)</f>
-        <v>201769.19967288416</v>
+        <v>30671.397228619629</v>
       </c>
       <c r="Q47" s="22">
         <f>+SUM(N47:$N$60)</f>
-        <v>10049.239816548512</v>
+        <v>1528.6867801202177</v>
       </c>
       <c r="R47" s="22">
         <f>+SUM(O47:$O$60)</f>
-        <v>19974.53424783735</v>
+        <v>15735.71756810537</v>
       </c>
       <c r="S47" s="22">
         <f>+SUM(P47:$P$60)</f>
-        <v>954178.18151918752</v>
+        <v>62674.945720802105</v>
       </c>
       <c r="T47" s="22">
         <f>+SUM(Q47:$Q$60)</f>
-        <v>47510.507607541527</v>
+        <v>3123.4829411073506</v>
       </c>
       <c r="U47" s="22">
         <f>+SUM(R47:$R$60)</f>
-        <v>39641.079756777275</v>
+        <v>15735.71756810537</v>
       </c>
       <c r="V47" s="23">
         <f t="shared" si="10"/>
-        <v>0.92870194145836482</v>
+        <v>0.96933062986930862</v>
       </c>
       <c r="W47" s="23"/>
       <c r="X47" s="14">
@@ -9629,28 +9629,26 @@
         <f t="shared" si="9"/>
         <v>3.3350000000000003E-4</v>
       </c>
-      <c r="D48" s="26">
-        <v>2E-3</v>
-      </c>
+      <c r="D48" s="26"/>
       <c r="E48" s="20">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F48" s="22">
         <f t="shared" si="11"/>
-        <v>7279215.4246243965</v>
+        <v>3336002.6399170971</v>
       </c>
       <c r="G48" s="22">
         <f t="shared" si="12"/>
-        <v>48495.726504291997</v>
+        <v>22247.4272310509</v>
       </c>
       <c r="H48" s="22">
         <f t="shared" si="13"/>
-        <v>2417.1027146976899</v>
+        <v>1108.8465032161801</v>
       </c>
       <c r="I48" s="22">
         <f t="shared" si="14"/>
-        <v>14507.458960129599</v>
+        <v>0</v>
       </c>
       <c r="J48" s="22">
         <f t="shared" si="15"/>
@@ -9658,7 +9656,7 @@
       </c>
       <c r="K48" s="4">
         <f t="shared" si="4"/>
-        <v>3447608.9864783594</v>
+        <v>1580009.9336786934</v>
       </c>
       <c r="L48" s="4">
         <f t="shared" si="5"/>
@@ -9666,43 +9664,43 @@
       </c>
       <c r="M48" s="4">
         <f t="shared" si="6"/>
-        <v>22257.700962840161</v>
+        <v>10210.726144239814</v>
       </c>
       <c r="N48" s="22">
         <f t="shared" si="7"/>
-        <v>1109.3585620466779</v>
+        <v>508.91853079244902</v>
       </c>
       <c r="O48" s="4">
         <f t="shared" si="8"/>
-        <v>6658.3739752133206</v>
+        <v>0</v>
       </c>
       <c r="P48" s="22">
         <f>+SUM(M48:$M$60)</f>
-        <v>180983.88428435463</v>
+        <v>21107.137318211142</v>
       </c>
       <c r="Q48" s="22">
         <f>+SUM(N48:$N$60)</f>
-        <v>9012.9808409609068</v>
+        <v>1051.8573458897908</v>
       </c>
       <c r="R48" s="22">
         <f>+SUM(O48:$O$60)</f>
-        <v>13162.459742076622</v>
+        <v>0</v>
       </c>
       <c r="S48" s="22">
         <f>+SUM(P48:$P$60)</f>
-        <v>752408.98184630345</v>
+        <v>32003.548492182472</v>
       </c>
       <c r="T48" s="22">
         <f>+SUM(Q48:$Q$60)</f>
-        <v>37461.267790993021</v>
+        <v>1594.7961609871327</v>
       </c>
       <c r="U48" s="22">
         <f>+SUM(R48:$R$60)</f>
-        <v>19666.545508939926</v>
+        <v>0</v>
       </c>
       <c r="V48" s="23">
         <f t="shared" si="10"/>
-        <v>0.93655009959209434</v>
+        <v>0.98542129282506319</v>
       </c>
       <c r="W48" s="23"/>
       <c r="X48" s="14">
@@ -9798,28 +9796,26 @@
         <f t="shared" si="9"/>
         <v>3.6350000000000005E-4</v>
       </c>
-      <c r="D49" s="26">
-        <v>2E-3</v>
-      </c>
+      <c r="D49" s="26"/>
       <c r="E49" s="20">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="F49" s="22">
         <f t="shared" si="11"/>
-        <v>7213795.1364452764</v>
+        <v>3312646.3661828297</v>
       </c>
       <c r="G49" s="22">
         <f t="shared" si="12"/>
-        <v>52382.324133240902</v>
+        <v>24078.562007970999</v>
       </c>
       <c r="H49" s="22">
         <f t="shared" si="13"/>
-        <v>2610.07009949141</v>
+        <v>1199.76987992928</v>
       </c>
       <c r="I49" s="22">
         <f t="shared" si="14"/>
-        <v>14372.5332994663</v>
+        <v>0</v>
       </c>
       <c r="J49" s="22">
         <f t="shared" si="15"/>
@@ -9827,7 +9823,7 @@
       </c>
       <c r="K49" s="4">
         <f t="shared" si="4"/>
-        <v>3368785.3435712978</v>
+        <v>1546979.684861209</v>
       </c>
       <c r="L49" s="4">
         <f t="shared" si="5"/>
@@ -9835,43 +9831,43 @@
       </c>
       <c r="M49" s="4">
         <f t="shared" si="6"/>
-        <v>23704.876637362428</v>
+        <v>10896.41117397133</v>
       </c>
       <c r="N49" s="22">
         <f t="shared" si="7"/>
-        <v>1181.1501445780573</v>
+        <v>542.93881509734183</v>
       </c>
       <c r="O49" s="4">
         <f t="shared" si="8"/>
-        <v>6504.0857668633025</v>
+        <v>0</v>
       </c>
       <c r="P49" s="22">
         <f>+SUM(M49:$M$60)</f>
-        <v>158726.18332151446</v>
+        <v>10896.41117397133</v>
       </c>
       <c r="Q49" s="22">
         <f>+SUM(N49:$N$60)</f>
-        <v>7903.6222789142284</v>
+        <v>542.93881509734183</v>
       </c>
       <c r="R49" s="22">
         <f>+SUM(O49:$O$60)</f>
-        <v>6504.0857668633025</v>
+        <v>0</v>
       </c>
       <c r="S49" s="22">
         <f>+SUM(P49:$P$60)</f>
-        <v>571425.09756194882</v>
+        <v>10896.41117397133</v>
       </c>
       <c r="T49" s="22">
         <f>+SUM(Q49:$Q$60)</f>
-        <v>28448.286950032118</v>
+        <v>542.93881509734183</v>
       </c>
       <c r="U49" s="22">
         <f>+SUM(R49:$R$60)</f>
-        <v>6504.0857668633025</v>
+        <v>0</v>
       </c>
       <c r="V49" s="23">
         <f t="shared" si="10"/>
-        <v>0.94504346213575119</v>
+        <v>0.99236914264499998</v>
       </c>
       <c r="W49" s="23"/>
       <c r="X49" s="14">
@@ -9960,29 +9956,24 @@
       <c r="A50" s="19">
         <v>55</v>
       </c>
-      <c r="B50" s="29">
-        <v>7.8899999999999994E-3</v>
-      </c>
-      <c r="C50" s="20">
-        <f t="shared" si="9"/>
-        <v>3.9449999999999999E-4</v>
-      </c>
+      <c r="B50" s="29"/>
+      <c r="C50" s="20"/>
       <c r="D50" s="30"/>
       <c r="E50" s="20">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" s="22">
         <f t="shared" si="11"/>
-        <v>7144430.2089130776</v>
+        <v>3287368.0342949294</v>
       </c>
       <c r="G50" s="22">
         <f t="shared" si="12"/>
-        <v>56358.435453728998</v>
+        <v>0</v>
       </c>
       <c r="H50" s="22">
         <f t="shared" si="13"/>
-        <v>2807.3588228210001</v>
+        <v>0</v>
       </c>
       <c r="I50" s="22">
         <f t="shared" si="14"/>
@@ -9990,23 +9981,23 @@
       </c>
       <c r="J50" s="22">
         <f t="shared" si="15"/>
-        <v>0</v>
+        <v>3287368.0342949298</v>
       </c>
       <c r="K50" s="4">
         <f t="shared" si="4"/>
-        <v>3289676.8216174771</v>
+        <v>1513679.6231916007</v>
       </c>
       <c r="L50" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1513679.6231916009</v>
       </c>
       <c r="M50" s="4">
         <f t="shared" si="6"/>
-        <v>25147.103355842686</v>
+        <v>0</v>
       </c>
       <c r="N50" s="22">
         <f t="shared" si="7"/>
-        <v>1252.6419852867907</v>
+        <v>0</v>
       </c>
       <c r="O50" s="4">
         <f t="shared" si="8"/>
@@ -10014,11 +10005,11 @@
       </c>
       <c r="P50" s="22">
         <f>+SUM(M50:$M$60)</f>
-        <v>135021.30668415205</v>
+        <v>0</v>
       </c>
       <c r="Q50" s="22">
         <f>+SUM(N50:$N$60)</f>
-        <v>6722.4721343361707</v>
+        <v>0</v>
       </c>
       <c r="R50" s="22">
         <f>+SUM(O50:$O$60)</f>
@@ -10026,11 +10017,11 @@
       </c>
       <c r="S50" s="22">
         <f>+SUM(P50:$P$60)</f>
-        <v>412698.91424043442</v>
+        <v>0</v>
       </c>
       <c r="T50" s="22">
         <f>+SUM(Q50:$Q$60)</f>
-        <v>20544.664671117887</v>
+        <v>0</v>
       </c>
       <c r="U50" s="22">
         <f>+SUM(R50:$R$60)</f>
@@ -10038,7 +10029,7 @@
       </c>
       <c r="V50" s="23">
         <f t="shared" si="10"/>
-        <v>0.95421884342564656</v>
+        <v>1</v>
       </c>
       <c r="W50" s="23"/>
       <c r="X50" s="14">
@@ -10127,13 +10118,8 @@
       <c r="A51" s="19">
         <v>56</v>
       </c>
-      <c r="B51" s="29">
-        <v>8.4700000000000001E-3</v>
-      </c>
-      <c r="C51" s="20">
-        <f t="shared" si="9"/>
-        <v>4.2350000000000005E-4</v>
-      </c>
+      <c r="B51" s="29"/>
+      <c r="C51" s="20"/>
       <c r="D51" s="30"/>
       <c r="E51" s="20">
         <f t="shared" si="3"/>
@@ -10141,15 +10127,15 @@
       </c>
       <c r="F51" s="22">
         <f t="shared" si="11"/>
-        <v>7085264.4146365281</v>
+        <v>0</v>
       </c>
       <c r="G51" s="22">
         <f t="shared" si="12"/>
-        <v>59999.482010825297</v>
+        <v>0</v>
       </c>
       <c r="H51" s="22">
         <f t="shared" si="13"/>
-        <v>2987.90189845247</v>
+        <v>0</v>
       </c>
       <c r="I51" s="22">
         <f t="shared" si="14"/>
@@ -10161,7 +10147,7 @@
       </c>
       <c r="K51" s="4">
         <f t="shared" si="4"/>
-        <v>3216753.6434485549</v>
+        <v>0</v>
       </c>
       <c r="L51" s="4">
         <f t="shared" si="5"/>
@@ -10169,11 +10155,11 @@
       </c>
       <c r="M51" s="4">
         <f t="shared" si="6"/>
-        <v>26396.882665431545</v>
+        <v>0</v>
       </c>
       <c r="N51" s="22">
         <f t="shared" si="7"/>
-        <v>1314.5329457184282</v>
+        <v>0</v>
       </c>
       <c r="O51" s="4">
         <f t="shared" si="8"/>
@@ -10181,11 +10167,11 @@
       </c>
       <c r="P51" s="22">
         <f>+SUM(M51:$M$60)</f>
-        <v>109874.20332830936</v>
+        <v>0</v>
       </c>
       <c r="Q51" s="22">
         <f>+SUM(N51:$N$60)</f>
-        <v>5469.8301490493805</v>
+        <v>0</v>
       </c>
       <c r="R51" s="22">
         <f>+SUM(O51:$O$60)</f>
@@ -10193,11 +10179,11 @@
       </c>
       <c r="S51" s="22">
         <f>+SUM(P51:$P$60)</f>
-        <v>277677.60755628237</v>
+        <v>0</v>
       </c>
       <c r="T51" s="22">
         <f>+SUM(Q51:$Q$60)</f>
-        <v>13822.192536781715</v>
+        <v>0</v>
       </c>
       <c r="U51" s="22">
         <f>+SUM(R51:$R$60)</f>
@@ -10205,7 +10191,7 @@
       </c>
       <c r="V51" s="23">
         <f t="shared" si="10"/>
-        <v>0.96218708744323067</v>
+        <v>0</v>
       </c>
       <c r="W51" s="3"/>
       <c r="X51" s="14">
@@ -10294,13 +10280,8 @@
       <c r="A52" s="19">
         <v>57</v>
       </c>
-      <c r="B52" s="29">
-        <v>8.9800000000000001E-3</v>
-      </c>
-      <c r="C52" s="20">
-        <f t="shared" si="9"/>
-        <v>4.4900000000000002E-4</v>
-      </c>
+      <c r="B52" s="29"/>
+      <c r="C52" s="20"/>
       <c r="D52" s="30"/>
       <c r="E52" s="20">
         <f t="shared" si="3"/>
@@ -10308,15 +10289,15 @@
       </c>
       <c r="F52" s="22">
         <f t="shared" si="11"/>
-        <v>7022277.0307272505</v>
+        <v>0</v>
       </c>
       <c r="G52" s="22">
         <f t="shared" si="12"/>
-        <v>63045.890755214001</v>
+        <v>0</v>
       </c>
       <c r="H52" s="22">
         <f t="shared" si="13"/>
-        <v>3138.8454060798199</v>
+        <v>0</v>
       </c>
       <c r="I52" s="22">
         <f t="shared" si="14"/>
@@ -10328,7 +10309,7 @@
       </c>
       <c r="K52" s="4">
         <f t="shared" si="4"/>
-        <v>3143516.9050618652</v>
+        <v>0</v>
       </c>
       <c r="L52" s="4">
         <f t="shared" si="5"/>
@@ -10336,11 +10317,11 @@
       </c>
       <c r="M52" s="4">
         <f t="shared" si="6"/>
-        <v>27348.784461850504</v>
+        <v>0</v>
       </c>
       <c r="N52" s="22">
         <f t="shared" si="7"/>
-        <v>1361.6051013260876</v>
+        <v>0</v>
       </c>
       <c r="O52" s="4">
         <f t="shared" si="8"/>
@@ -10348,11 +10329,11 @@
       </c>
       <c r="P52" s="22">
         <f>+SUM(M52:$M$60)</f>
-        <v>83477.320662877813</v>
+        <v>0</v>
       </c>
       <c r="Q52" s="22">
         <f>+SUM(N52:$N$60)</f>
-        <v>4155.2972033309525</v>
+        <v>0</v>
       </c>
       <c r="R52" s="22">
         <f>+SUM(O52:$O$60)</f>
@@ -10360,11 +10341,11 @@
       </c>
       <c r="S52" s="22">
         <f>+SUM(P52:$P$60)</f>
-        <v>167803.40422797299</v>
+        <v>0</v>
       </c>
       <c r="T52" s="22">
         <f>+SUM(Q52:$Q$60)</f>
-        <v>8352.3623877323353</v>
+        <v>0</v>
       </c>
       <c r="U52" s="22">
         <f>+SUM(R52:$R$60)</f>
@@ -10372,7 +10353,7 @@
       </c>
       <c r="V52" s="23">
         <f t="shared" si="10"/>
-        <v>0.97081757114590228</v>
+        <v>0</v>
       </c>
       <c r="W52" s="3"/>
       <c r="X52" s="14">
@@ -10461,13 +10442,8 @@
       <c r="A53" s="19">
         <v>58</v>
       </c>
-      <c r="B53" s="29">
-        <v>9.3900000000000008E-3</v>
-      </c>
-      <c r="C53" s="20">
-        <f t="shared" si="9"/>
-        <v>4.6950000000000008E-4</v>
-      </c>
+      <c r="B53" s="29"/>
+      <c r="C53" s="20"/>
       <c r="D53" s="31"/>
       <c r="E53" s="20">
         <f t="shared" si="3"/>
@@ -10475,15 +10451,15 @@
       </c>
       <c r="F53" s="22">
         <f t="shared" si="11"/>
-        <v>6956092.294565957</v>
+        <v>0</v>
       </c>
       <c r="G53" s="22">
         <f t="shared" si="12"/>
-        <v>65302.373314339202</v>
+        <v>0</v>
       </c>
       <c r="H53" s="22">
         <f t="shared" si="13"/>
-        <v>3250.5520006635702</v>
+        <v>0</v>
       </c>
       <c r="I53" s="22">
         <f t="shared" si="14"/>
@@ -10495,7 +10471,7 @@
       </c>
       <c r="K53" s="4">
         <f t="shared" si="4"/>
-        <v>3070289.1641244171</v>
+        <v>0</v>
       </c>
       <c r="L53" s="4">
         <f t="shared" si="5"/>
@@ -10503,11 +10479,11 @@
       </c>
       <c r="M53" s="4">
         <f t="shared" si="6"/>
-        <v>27930.98883695943</v>
+        <v>0</v>
       </c>
       <c r="N53" s="22">
         <f t="shared" si="7"/>
-        <v>1390.3190196083465</v>
+        <v>0</v>
       </c>
       <c r="O53" s="4">
         <f t="shared" si="8"/>
@@ -10515,11 +10491,11 @@
       </c>
       <c r="P53" s="22">
         <f>+SUM(M53:$M$60)</f>
-        <v>56128.536201027309</v>
+        <v>0</v>
       </c>
       <c r="Q53" s="22">
         <f>+SUM(N53:$N$60)</f>
-        <v>2793.6921020048649</v>
+        <v>0</v>
       </c>
       <c r="R53" s="22">
         <f>+SUM(O53:$O$60)</f>
@@ -10527,11 +10503,11 @@
       </c>
       <c r="S53" s="22">
         <f>+SUM(P53:$P$60)</f>
-        <v>84326.083565095192</v>
+        <v>0</v>
       </c>
       <c r="T53" s="22">
         <f>+SUM(Q53:$Q$60)</f>
-        <v>4197.0651844013828</v>
+        <v>0</v>
       </c>
       <c r="U53" s="22">
         <f>+SUM(R53:$R$60)</f>
@@ -10539,7 +10515,7 @@
       </c>
       <c r="V53" s="23">
         <f t="shared" si="10"/>
-        <v>0.98005455393539653</v>
+        <v>0</v>
       </c>
       <c r="W53" s="3"/>
       <c r="X53" s="14">
@@ -10628,13 +10604,8 @@
       <c r="A54" s="19">
         <v>59</v>
       </c>
-      <c r="B54" s="29">
-        <v>9.7099999999999999E-3</v>
-      </c>
-      <c r="C54" s="20">
-        <f t="shared" si="9"/>
-        <v>4.8550000000000004E-4</v>
-      </c>
+      <c r="B54" s="29"/>
+      <c r="C54" s="20"/>
       <c r="D54" s="31"/>
       <c r="E54" s="20">
         <f t="shared" si="3"/>
@@ -10642,15 +10613,15 @@
       </c>
       <c r="F54" s="22">
         <f t="shared" si="11"/>
-        <v>6887539.3692509541</v>
+        <v>0</v>
       </c>
       <c r="G54" s="22">
         <f t="shared" si="12"/>
-        <v>66861.772639160699</v>
+        <v>0</v>
       </c>
       <c r="H54" s="22">
         <f t="shared" si="13"/>
-        <v>3327.6657275052298</v>
+        <v>0</v>
       </c>
       <c r="I54" s="22">
         <f t="shared" si="14"/>
@@ -10662,7 +10633,7 @@
       </c>
       <c r="K54" s="4">
         <f t="shared" si="4"/>
-        <v>2997465.1397268395</v>
+        <v>0</v>
       </c>
       <c r="L54" s="4">
         <f t="shared" si="5"/>
@@ -10670,11 +10641,11 @@
       </c>
       <c r="M54" s="4">
         <f t="shared" si="6"/>
-        <v>28197.547364067879</v>
+        <v>0</v>
       </c>
       <c r="N54" s="22">
         <f t="shared" si="7"/>
-        <v>1403.3730823965182</v>
+        <v>0</v>
       </c>
       <c r="O54" s="4">
         <f t="shared" si="8"/>
@@ -10682,11 +10653,11 @@
       </c>
       <c r="P54" s="22">
         <f>+SUM(M54:$M$60)</f>
-        <v>28197.547364067879</v>
+        <v>0</v>
       </c>
       <c r="Q54" s="22">
         <f>+SUM(N54:$N$60)</f>
-        <v>1403.3730823965182</v>
+        <v>0</v>
       </c>
       <c r="R54" s="22">
         <f>+SUM(O54:$O$60)</f>
@@ -10694,11 +10665,11 @@
       </c>
       <c r="S54" s="22">
         <f>+SUM(P54:$P$60)</f>
-        <v>28197.547364067879</v>
+        <v>0</v>
       </c>
       <c r="T54" s="22">
         <f>+SUM(Q54:$Q$60)</f>
-        <v>1403.3730823965182</v>
+        <v>0</v>
       </c>
       <c r="U54" s="22">
         <f>+SUM(R54:$R$60)</f>
@@ -10706,7 +10677,7 @@
       </c>
       <c r="V54" s="23">
         <f t="shared" si="10"/>
-        <v>0.9898092142049999</v>
+        <v>0</v>
       </c>
       <c r="W54" s="3"/>
       <c r="X54" s="14">
@@ -10806,11 +10777,11 @@
       <c r="D55" s="31"/>
       <c r="E55" s="20">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F55" s="22">
         <f t="shared" si="11"/>
-        <v>6817349.9308842877</v>
+        <v>0</v>
       </c>
       <c r="G55" s="22">
         <f t="shared" si="12"/>
@@ -10826,15 +10797,15 @@
       </c>
       <c r="J55" s="22">
         <f t="shared" si="15"/>
-        <v>6817349.9308842896</v>
+        <v>0</v>
       </c>
       <c r="K55" s="4">
         <f t="shared" si="4"/>
-        <v>2925376.2813133607</v>
+        <v>0</v>
       </c>
       <c r="L55" s="4">
         <f t="shared" si="5"/>
-        <v>2925376.2813133616</v>
+        <v>0</v>
       </c>
       <c r="M55" s="4">
         <f t="shared" si="6"/>
@@ -10874,7 +10845,7 @@
       </c>
       <c r="V55" s="23">
         <f t="shared" si="10"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W55" s="3"/>
       <c r="X55" s="14">
